--- a/Plan_RNC.xlsx
+++ b/Plan_RNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\AUTO-RNC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CB21F4-0D53-4944-AE38-89D2106E6902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0915D352-746C-4E15-983D-67667789C21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
   <si>
     <t>NUMERO-NF</t>
   </si>
@@ -162,15 +162,6 @@
     <t>RESPONSAVEL</t>
   </si>
   <si>
-    <t>DEVOLUÇÃO CLIENTE</t>
-  </si>
-  <si>
-    <t>69468/25</t>
-  </si>
-  <si>
-    <t>LOADER CX02X10KG</t>
-  </si>
-  <si>
     <t>KG</t>
   </si>
   <si>
@@ -195,9 +186,6 @@
     <t>Big Bag</t>
   </si>
   <si>
-    <t>DEVOLUÇÃO</t>
-  </si>
-  <si>
     <t>PASTA-ANEXOS</t>
   </si>
   <si>
@@ -222,53 +210,41 @@
     <t>RESUMO-RAPIDO</t>
   </si>
   <si>
-    <t>*DESLIGAR NUM-LOCK</t>
-  </si>
-  <si>
-    <t>Hortolândia</t>
-  </si>
-  <si>
-    <t>a01</t>
-  </si>
-  <si>
-    <t>Durante a descarga da devolução proveniente do cliente Carlos Tamotsu Kogio, realizada no veículo placa ODO0C67, foi identificada a seguinte não conformidade: A) O produto LOADER CX02X10KG (NF 594, Lote 69468/25) apresentou 3 (três) caixas rasgadas, totalizando 60kg na movimentação. No momento da inspeção, constatou-se que, apesar do dano nas embalagens secundárias (caixas), o produto interno não foi avariado. A ressalva é necessária devido à descaracterização da embalagem padrão Nitro.</t>
-  </si>
-  <si>
-    <t>03 caixas rasgadas</t>
-  </si>
-  <si>
-    <t>50kg do produto faltando</t>
-  </si>
-  <si>
-    <t>a02</t>
-  </si>
-  <si>
-    <t>ASCU0350PB</t>
-  </si>
-  <si>
-    <t>FERTICOBRE 35 A SCX25KG</t>
-  </si>
-  <si>
-    <t>VZP TRANSF HORT</t>
-  </si>
-  <si>
     <t>VZP NITRO</t>
   </si>
   <si>
-    <t>0511/25</t>
-  </si>
-  <si>
-    <t>Durante o recebimento proveniente da unidade VZP NITRO, realizado pela transportadora MMCM TRANSPORTES, veículo placa CSK4B33, foi identificada a seguinte não conformidade: A) O produto FERTICOBRE 35 A SCX25KG (NF 10605, Lote 0511/25) apresentou uma divergência no ato da descarga, totalizando a falta de 50kg (2 sacos). No momento da conferência física da carga, constatou-se a ausência dos volumes em relação ao faturamento da nota fiscal, caracterizando a falta do produto no ato da entrega.</t>
-  </si>
-  <si>
     <t>NITRO</t>
+  </si>
+  <si>
+    <t>DATA DE FRABRICAÇÃO DIVERGENTE</t>
+  </si>
+  <si>
+    <t>00104</t>
+  </si>
+  <si>
+    <t>SPEED GRAMINEA SCX25KG</t>
+  </si>
+  <si>
+    <t>74771/26</t>
+  </si>
+  <si>
+    <t>a05</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>VZP TRANSF CBA</t>
+  </si>
+  <si>
+    <t>Durante o recebimento proveniente da unidade NITRO VZP, realizado pela transportadora MMCM, veículo placa SUF-2B15, foi identificada a seguinte não conformidade: A) O produto SPEED GRAMINEA SCX25KG (NF 10670, Lote 74771/26) apresentou divergência na informação de data de fabricação. No momento da conferência física, constatou-se que a data gravada nas sacarias é 04/03/2026, enquanto o documento fiscal (NF) indica a data de 06/03/2026. Esta inconsistência entre o físico e o faturado compromete a rastreabilidade e o padrão de conformidade Nitro.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,14 +306,6 @@
       <family val="1"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
@@ -351,6 +319,39 @@
       <family val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <u/>
       <sz val="12"/>
       <color rgb="FFFFC000"/>
@@ -360,14 +361,15 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -447,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -472,12 +474,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -489,14 +485,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -505,10 +498,30 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -516,7 +529,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -793,672 +817,633 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W19"/>
-  <sheetFormatPr defaultColWidth="25.77734375" defaultRowHeight="19.95" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="19.95" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="22" width="25.77734375" style="1"/>
-    <col min="24" max="16384" width="25.77734375" style="1"/>
+    <col min="1" max="22" width="25.77734375" style="1" customWidth="1"/>
+    <col min="23" max="23" width="0" hidden="1" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="19" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:23" s="16" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="S1" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="T1" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="V1" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="17"/>
+    </row>
+    <row r="2" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="18">
+        <v>355</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="11" t="s">
+      <c r="E2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="10">
+        <v>10670</v>
+      </c>
+      <c r="J2" s="11">
+        <v>46087</v>
+      </c>
+      <c r="K2" s="11">
+        <v>46816</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M2" s="11">
+        <v>46085</v>
+      </c>
+      <c r="N2" s="11">
+        <v>46816</v>
+      </c>
+      <c r="O2" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="24">
+        <v>30000</v>
+      </c>
+      <c r="Q2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="T2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="12" t="str">
+        <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>PROCESSO</v>
+      </c>
+      <c r="W2"/>
+    </row>
+    <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="15"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="12">
+        <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="J1" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="L1" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="N1" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="O1" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="P1" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="S1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="U1" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="V1" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="W1" s="20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="21">
-        <v>349</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="12">
-        <v>989</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="12">
-        <v>594</v>
-      </c>
-      <c r="J2" s="13">
-        <v>45849</v>
-      </c>
-      <c r="K2" s="13">
-        <v>46945</v>
-      </c>
-      <c r="L2" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="13">
-        <v>45849</v>
-      </c>
-      <c r="N2" s="13">
-        <v>46945</v>
-      </c>
-      <c r="O2" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" s="12">
-        <v>60</v>
-      </c>
-      <c r="Q2" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="T2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="U2" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="V2" s="14" t="str">
-        <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>AVARIA</v>
-      </c>
-      <c r="W2"/>
-    </row>
-    <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="21">
-        <v>350</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="12">
-        <v>10605</v>
-      </c>
-      <c r="J3" s="13">
-        <v>45866</v>
-      </c>
-      <c r="K3" s="13">
-        <v>46596</v>
-      </c>
-      <c r="L3" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="M3" s="13">
-        <v>45866</v>
-      </c>
-      <c r="N3" s="13">
-        <v>46596</v>
-      </c>
-      <c r="O3" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="P3" s="12">
-        <v>50</v>
-      </c>
-      <c r="Q3" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="S3" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="T3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="V3" s="14" t="str">
-        <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
-      </c>
       <c r="W3"/>
     </row>
     <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="14">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="12">
         <f>IF(B4="",0,VLOOKUP(T4,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W4"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="14">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="12">
         <f>IF(B5="",0,VLOOKUP(T5,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W5"/>
     </row>
-    <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="12"/>
-      <c r="T6" s="12"/>
-      <c r="U6" s="12"/>
-      <c r="V6" s="14">
+    <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="12">
         <f>IF(B6="",0,VLOOKUP(T6,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W6"/>
     </row>
-    <row r="7" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="12"/>
-      <c r="R7" s="12"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="12"/>
-      <c r="U7" s="12"/>
-      <c r="V7" s="14">
+    <row r="7" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="12">
         <f>IF(B7="",0,VLOOKUP(T7,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W7"/>
     </row>
-    <row r="8" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="14">
+    <row r="8" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="12">
         <f>IF(B8="",0,VLOOKUP(T8,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W8"/>
     </row>
-    <row r="9" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
-      <c r="T9" s="12"/>
-      <c r="U9" s="12"/>
-      <c r="V9" s="14">
+    <row r="9" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="12">
         <f>IF(B9="",0,VLOOKUP(T9,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W9"/>
     </row>
-    <row r="10" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
-      <c r="Q10" s="12"/>
-      <c r="R10" s="12"/>
-      <c r="S10" s="12"/>
-      <c r="T10" s="12"/>
-      <c r="U10" s="12"/>
-      <c r="V10" s="14">
+    <row r="10" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="12">
         <f>IF(B10="",0,VLOOKUP(T10,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W10"/>
     </row>
-    <row r="11" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
-      <c r="Q11" s="12"/>
-      <c r="R11" s="12"/>
-      <c r="S11" s="12"/>
-      <c r="T11" s="12"/>
-      <c r="U11" s="12"/>
-      <c r="V11" s="14">
+    <row r="11" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="12">
         <f>IF(B11="",0,VLOOKUP(T11,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W11"/>
     </row>
-    <row r="12" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
-      <c r="Q12" s="12"/>
-      <c r="R12" s="12"/>
-      <c r="S12" s="12"/>
-      <c r="T12" s="12"/>
-      <c r="U12" s="12"/>
-      <c r="V12" s="14">
+    <row r="12" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="12">
         <f>IF(B12="",0,VLOOKUP(T12,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W12"/>
     </row>
-    <row r="13" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="14">
+    <row r="13" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="12">
         <f>IF(B13="",0,VLOOKUP(T13,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W13"/>
     </row>
-    <row r="14" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="12"/>
-      <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
-      <c r="Q14" s="12"/>
-      <c r="R14" s="12"/>
-      <c r="S14" s="12"/>
-      <c r="T14" s="12"/>
-      <c r="U14" s="12"/>
-      <c r="V14" s="14">
+    <row r="14" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="12">
         <f>IF(B14="",0,VLOOKUP(T14,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W14"/>
     </row>
-    <row r="15" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="12"/>
-      <c r="O15" s="12"/>
-      <c r="P15" s="12"/>
-      <c r="Q15" s="12"/>
-      <c r="R15" s="12"/>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="14">
+    <row r="15" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="12">
         <f>IF(B15="",0,VLOOKUP(T15,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W15"/>
     </row>
-    <row r="16" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="12"/>
-      <c r="N16" s="12"/>
-      <c r="O16" s="12"/>
-      <c r="P16" s="12"/>
-      <c r="Q16" s="12"/>
-      <c r="R16" s="12"/>
-      <c r="S16" s="12"/>
-      <c r="T16" s="12"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="14">
+    <row r="16" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="12">
         <f>IF(B16="",0,VLOOKUP(T16,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W16"/>
     </row>
-    <row r="17" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="14">
+    <row r="17" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="12">
         <f>IF(B17="",0,VLOOKUP(T17,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W17"/>
     </row>
-    <row r="18" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="21"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="14">
+    <row r="18" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="12">
         <f>IF(B18="",0,VLOOKUP(T18,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W18"/>
     </row>
-    <row r="19" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="21"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="21"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="14">
+    <row r="19" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="12">
         <f>IF(B19="",0,VLOOKUP(T19,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W19"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="17" type="noConversion"/>
+  <conditionalFormatting sqref="I1:I1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q19" xr:uid="{AEBEAE45-30D1-4542-A1D6-EBC88D16BDC1}">
       <formula1>"KG, L, Ds"</formula1>
@@ -1513,9 +1498,9 @@
         <v>30</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1523,7 +1508,7 @@
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="14" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="6"/>
@@ -1532,56 +1517,56 @@
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="16"/>
+        <v>35</v>
+      </c>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>46</v>
+      <c r="B4" s="14" t="s">
+        <v>42</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>46</v>
+      <c r="B5" s="14" t="s">
+        <v>42</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>46</v>
+      <c r="B6" s="14" t="s">
+        <v>42</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>46</v>
+      <c r="B7" s="14" t="s">
+        <v>42</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F7"/>
     </row>
@@ -1589,11 +1574,11 @@
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F8"/>
     </row>
@@ -1601,7 +1586,7 @@
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D9"/>
@@ -1611,7 +1596,7 @@
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D10"/>
@@ -1621,7 +1606,7 @@
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D11"/>
@@ -1631,7 +1616,7 @@
       <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="14" t="s">
         <v>27</v>
       </c>
       <c r="D12"/>
@@ -1641,7 +1626,7 @@
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D13"/>
@@ -1651,7 +1636,7 @@
       <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="14" t="s">
         <v>28</v>
       </c>
       <c r="D14"/>

--- a/Plan_RNC.xlsx
+++ b/Plan_RNC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\AUTO-RNC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\RNC-RA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0915D352-746C-4E15-983D-67667789C21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291D0F20-7480-4C2F-88E0-7FD3D61DF802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -210,41 +210,41 @@
     <t>RESUMO-RAPIDO</t>
   </si>
   <si>
-    <t>VZP NITRO</t>
-  </si>
-  <si>
     <t>NITRO</t>
   </si>
   <si>
-    <t>DATA DE FRABRICAÇÃO DIVERGENTE</t>
-  </si>
-  <si>
-    <t>00104</t>
-  </si>
-  <si>
-    <t>SPEED GRAMINEA SCX25KG</t>
-  </si>
-  <si>
-    <t>74771/26</t>
-  </si>
-  <si>
-    <t>a05</t>
-  </si>
-  <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>VZP TRANSF CBA</t>
-  </si>
-  <si>
-    <t>Durante o recebimento proveniente da unidade NITRO VZP, realizado pela transportadora MMCM, veículo placa SUF-2B15, foi identificada a seguinte não conformidade: A) O produto SPEED GRAMINEA SCX25KG (NF 10670, Lote 74771/26) apresentou divergência na informação de data de fabricação. No momento da conferência física, constatou-se que a data gravada nas sacarias é 04/03/2026, enquanto o documento fiscal (NF) indica a data de 06/03/2026. Esta inconsistência entre o físico e o faturado compromete a rastreabilidade e o padrão de conformidade Nitro.</t>
+    <t>Caixas amassadas</t>
+  </si>
+  <si>
+    <t>a01</t>
+  </si>
+  <si>
+    <t>03824</t>
+  </si>
+  <si>
+    <t>SPEED CX02X10KG</t>
+  </si>
+  <si>
+    <t>HORT TRANSF CBA</t>
+  </si>
+  <si>
+    <t>HORT</t>
+  </si>
+  <si>
+    <t>69177/25</t>
+  </si>
+  <si>
+    <t>Durante a descarga da transferência proveniente da unidade de Hortolândia para a unidade de Cuiabá, realizada pela transportadora Fantinato, veículo placa FTG0F13, foi identificada a seguinte não conformidade: A) O produto SPEED CX02X10KG (NF 10817, Lote 69177/25) apresentou caixas amassadas no momento da conferência. A avaria na embalagem secundária caracteriza o descumprimento do padrão Nitro de transporte e integridade da carga, sendo necessária a ressalva para registro de qualidade.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,10 +342,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FFFFFF00"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -354,22 +351,7 @@
       <b/>
       <u/>
       <sz val="12"/>
-      <color rgb="FFFFC000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
+      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -381,12 +363,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -409,6 +385,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -449,17 +431,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -485,7 +467,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -495,27 +477,9 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -524,6 +488,18 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -819,12 +795,13 @@
   <dimension ref="A1:W19"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="19.95" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="22" width="25.77734375" style="1" customWidth="1"/>
+    <col min="1" max="21" width="25.77734375" style="1" customWidth="1"/>
+    <col min="22" max="22" width="25.77734375" style="1" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="0" hidden="1" customWidth="1"/>
     <col min="24" max="16384" width="8.88671875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="16" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" s="22" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>48</v>
       </c>
@@ -834,13 +811,13 @@
       <c r="C1" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="20" t="s">
@@ -861,113 +838,113 @@
       <c r="L1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="19" t="s">
+      <c r="T1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="U1" s="19" t="s">
+      <c r="U1" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="V1" s="19" t="s">
+      <c r="V1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="17"/>
+      <c r="W1" s="21"/>
     </row>
     <row r="2" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="18">
-        <v>355</v>
-      </c>
-      <c r="C2" s="18" t="s">
+      <c r="B2" s="16">
+        <v>356</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2" s="10" t="s">
+      <c r="I2" s="10">
+        <v>10817</v>
+      </c>
+      <c r="J2" s="11">
+        <v>45842</v>
+      </c>
+      <c r="K2" s="11">
+        <v>46938</v>
+      </c>
+      <c r="L2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="10">
-        <v>10670</v>
-      </c>
-      <c r="J2" s="11">
-        <v>46087</v>
-      </c>
-      <c r="K2" s="11">
-        <v>46816</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="M2" s="11">
-        <v>46085</v>
+        <v>45842</v>
       </c>
       <c r="N2" s="11">
-        <v>46816</v>
-      </c>
-      <c r="O2" s="23" t="s">
-        <v>54</v>
-      </c>
-      <c r="P2" s="24">
-        <v>30000</v>
+        <v>46938</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="P2" s="18">
+        <v>9800</v>
       </c>
       <c r="Q2" s="10" t="s">
         <v>33</v>
       </c>
       <c r="R2" s="10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="S2" s="15" t="s">
         <v>58</v>
       </c>
       <c r="T2" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U2" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V2" s="12" t="str">
         <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
+        <v xml:space="preserve">EMBALAGEM </v>
       </c>
       <c r="W2"/>
     </row>
     <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="23"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -978,8 +955,8 @@
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="24"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="18"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
       <c r="S3" s="15"/>
@@ -992,10 +969,10 @@
       <c r="W3"/>
     </row>
     <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="23"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
@@ -1006,8 +983,8 @@
       <c r="L4" s="10"/>
       <c r="M4" s="11"/>
       <c r="N4" s="11"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="24"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="18"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
       <c r="S4" s="15"/>
@@ -1019,11 +996,11 @@
       </c>
       <c r="W4"/>
     </row>
-    <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="23"/>
+    <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
@@ -1034,8 +1011,8 @@
       <c r="L5" s="10"/>
       <c r="M5" s="10"/>
       <c r="N5" s="10"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="24"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="18"/>
       <c r="Q5" s="10"/>
       <c r="R5" s="10"/>
       <c r="S5" s="15"/>
@@ -1048,10 +1025,10 @@
       <c r="W5"/>
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="23"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
@@ -1062,8 +1039,8 @@
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
       <c r="N6" s="10"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="24"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="18"/>
       <c r="Q6" s="10"/>
       <c r="R6" s="10"/>
       <c r="S6" s="15"/>
@@ -1076,10 +1053,10 @@
       <c r="W6"/>
     </row>
     <row r="7" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="23"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="10"/>
@@ -1090,8 +1067,8 @@
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
       <c r="N7" s="10"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="24"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="18"/>
       <c r="Q7" s="10"/>
       <c r="R7" s="10"/>
       <c r="S7" s="10"/>
@@ -1104,10 +1081,10 @@
       <c r="W7"/>
     </row>
     <row r="8" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="23"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
@@ -1118,8 +1095,8 @@
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="24"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="18"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
       <c r="S8" s="10"/>
@@ -1132,10 +1109,10 @@
       <c r="W8"/>
     </row>
     <row r="9" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="23"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
@@ -1146,8 +1123,8 @@
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
       <c r="N9" s="10"/>
-      <c r="O9" s="23"/>
-      <c r="P9" s="24"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="18"/>
       <c r="Q9" s="10"/>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
@@ -1160,10 +1137,10 @@
       <c r="W9"/>
     </row>
     <row r="10" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="23"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="10"/>
@@ -1174,8 +1151,8 @@
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
       <c r="N10" s="10"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="24"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="18"/>
       <c r="Q10" s="10"/>
       <c r="R10" s="10"/>
       <c r="S10" s="10"/>
@@ -1188,10 +1165,10 @@
       <c r="W10"/>
     </row>
     <row r="11" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="23"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
@@ -1202,8 +1179,8 @@
       <c r="L11" s="10"/>
       <c r="M11" s="10"/>
       <c r="N11" s="10"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="24"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="18"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
@@ -1216,10 +1193,10 @@
       <c r="W11"/>
     </row>
     <row r="12" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="23"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -1230,8 +1207,8 @@
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="24"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="18"/>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
@@ -1244,10 +1221,10 @@
       <c r="W12"/>
     </row>
     <row r="13" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="23"/>
+      <c r="A13" s="16"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -1258,8 +1235,8 @@
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
       <c r="N13" s="10"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="24"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="18"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
@@ -1272,10 +1249,10 @@
       <c r="W13"/>
     </row>
     <row r="14" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="23"/>
+      <c r="A14" s="16"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -1286,8 +1263,8 @@
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
       <c r="N14" s="10"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="24"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="18"/>
       <c r="Q14" s="10"/>
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
@@ -1300,10 +1277,10 @@
       <c r="W14"/>
     </row>
     <row r="15" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="23"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="10"/>
@@ -1314,8 +1291,8 @@
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
       <c r="N15" s="10"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="24"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="18"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
@@ -1328,10 +1305,10 @@
       <c r="W15"/>
     </row>
     <row r="16" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="23"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -1342,8 +1319,8 @@
       <c r="L16" s="10"/>
       <c r="M16" s="10"/>
       <c r="N16" s="10"/>
-      <c r="O16" s="23"/>
-      <c r="P16" s="24"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="18"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
@@ -1356,10 +1333,10 @@
       <c r="W16"/>
     </row>
     <row r="17" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="23"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
@@ -1370,8 +1347,8 @@
       <c r="L17" s="10"/>
       <c r="M17" s="10"/>
       <c r="N17" s="10"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="24"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="18"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
       <c r="S17" s="10"/>
@@ -1384,10 +1361,10 @@
       <c r="W17"/>
     </row>
     <row r="18" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="23"/>
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -1398,8 +1375,8 @@
       <c r="L18" s="10"/>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
-      <c r="O18" s="23"/>
-      <c r="P18" s="24"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="18"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
       <c r="S18" s="10"/>
@@ -1412,10 +1389,10 @@
       <c r="W18"/>
     </row>
     <row r="19" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="23"/>
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
@@ -1426,8 +1403,8 @@
       <c r="L19" s="10"/>
       <c r="M19" s="10"/>
       <c r="N19" s="10"/>
-      <c r="O19" s="23"/>
-      <c r="P19" s="24"/>
+      <c r="O19" s="17"/>
+      <c r="P19" s="18"/>
       <c r="Q19" s="10"/>
       <c r="R19" s="10"/>
       <c r="S19" s="10"/>
@@ -1440,7 +1417,8 @@
       <c r="W19"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/Plan_RNC.xlsx
+++ b/Plan_RNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\RNC-RA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291D0F20-7480-4C2F-88E0-7FD3D61DF802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B667EE4E-1C3E-4B6C-8AF5-93F925068D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="81">
   <si>
     <t>NUMERO-NF</t>
   </si>
@@ -162,89 +162,157 @@
     <t>RESPONSAVEL</t>
   </si>
   <si>
+    <t>Embalagem</t>
+  </si>
+  <si>
+    <t>Saco</t>
+  </si>
+  <si>
+    <t>Bombona</t>
+  </si>
+  <si>
+    <t>Palete</t>
+  </si>
+  <si>
+    <t>Caixa</t>
+  </si>
+  <si>
+    <t>Galão</t>
+  </si>
+  <si>
+    <t>Big Bag</t>
+  </si>
+  <si>
+    <t>PASTA-ANEXOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMBALAGEM </t>
+  </si>
+  <si>
+    <t>NF-DATA-VALIDADE</t>
+  </si>
+  <si>
+    <t>NF-DATA-FABRICACAO</t>
+  </si>
+  <si>
+    <t>REAL-LOTE</t>
+  </si>
+  <si>
+    <t>REAL-DATA-FABRICACAO</t>
+  </si>
+  <si>
+    <t>REAL-DATA-VALIDADE</t>
+  </si>
+  <si>
+    <t>RESUMO-RAPIDO</t>
+  </si>
+  <si>
+    <t>DATA FABRICAÇÃO DIVERGENTE</t>
+  </si>
+  <si>
+    <t>rnc-01</t>
+  </si>
+  <si>
+    <t>05272</t>
+  </si>
+  <si>
+    <t>Hortolândia</t>
+  </si>
+  <si>
+    <t>NITRO 25-01 CX02X05L</t>
+  </si>
+  <si>
+    <t>CBA TRANSF HORT</t>
+  </si>
+  <si>
+    <t>002-24</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>NITRO</t>
+  </si>
+  <si>
+    <t>Durante a descarga da transferência proveniente da unidade de Cuiabá para Hortolândia, realizada pela transportadora Fantinato, veículo placa SUF2B15, foi identificada a seguinte não conformidade: A) O produto NITRO 25-01 CX02X05L (NF 5009, Lote 002-24) apresentou divergência na informação de data de fabricação, totalizando 210L envolvidos na movimentação. No momento da conferência física, constatou-se que a data gravada nas embalagens não condiz com o informado no documento fiscal, comprometendo a rastreabilidade do lote e o padrão de conformidade Nitro.</t>
+  </si>
+  <si>
+    <t>DATAS DIVERGENTES E LOTE NÃO CONSTA NA NF</t>
+  </si>
+  <si>
+    <t>rnc-02</t>
+  </si>
+  <si>
+    <t>00104</t>
+  </si>
+  <si>
+    <t>SPEED GRAMINEA SCX25KG</t>
+  </si>
+  <si>
+    <t>VZP TRANSF HORT</t>
+  </si>
+  <si>
+    <t>CUIABÁ</t>
+  </si>
+  <si>
+    <t>VZP NITRO</t>
+  </si>
+  <si>
+    <t>Lote WMS</t>
+  </si>
+  <si>
+    <t>75355/26</t>
+  </si>
+  <si>
     <t>KG</t>
   </si>
   <si>
-    <t>Embalagem</t>
-  </si>
-  <si>
-    <t>Saco</t>
-  </si>
-  <si>
-    <t>Bombona</t>
-  </si>
-  <si>
-    <t>Palete</t>
-  </si>
-  <si>
-    <t>Caixa</t>
-  </si>
-  <si>
-    <t>Galão</t>
-  </si>
-  <si>
-    <t>Big Bag</t>
-  </si>
-  <si>
-    <t>PASTA-ANEXOS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMBALAGEM </t>
-  </si>
-  <si>
-    <t>NF-DATA-VALIDADE</t>
-  </si>
-  <si>
-    <t>NF-DATA-FABRICACAO</t>
-  </si>
-  <si>
-    <t>REAL-LOTE</t>
-  </si>
-  <si>
-    <t>REAL-DATA-FABRICACAO</t>
-  </si>
-  <si>
-    <t>REAL-DATA-VALIDADE</t>
-  </si>
-  <si>
-    <t>RESUMO-RAPIDO</t>
-  </si>
-  <si>
-    <t>NITRO</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Caixas amassadas</t>
-  </si>
-  <si>
-    <t>a01</t>
-  </si>
-  <si>
-    <t>03824</t>
-  </si>
-  <si>
-    <t>SPEED CX02X10KG</t>
-  </si>
-  <si>
-    <t>HORT TRANSF CBA</t>
-  </si>
-  <si>
-    <t>HORT</t>
-  </si>
-  <si>
-    <t>69177/25</t>
-  </si>
-  <si>
-    <t>Durante a descarga da transferência proveniente da unidade de Hortolândia para a unidade de Cuiabá, realizada pela transportadora Fantinato, veículo placa FTG0F13, foi identificada a seguinte não conformidade: A) O produto SPEED CX02X10KG (NF 10817, Lote 69177/25) apresentou caixas amassadas no momento da conferência. A avaria na embalagem secundária caracteriza o descumprimento do padrão Nitro de transporte e integridade da carga, sendo necessária a ressalva para registro de qualidade.</t>
+    <t>Durante recebimento proveniente da unidade de VZP para Hortolândia, realizado pela transportadora MMCM, veículo placa EF08D60, foram identificadas inconformidades na documentação fiscal: A) O produto SPEED GRAMINEA SCX25KG (NF 10706), totalizando 30.000kg, apresentou divergência crítica de rastreabilidade. No momento da conferência física, constatou-se que a informação de Lote não consta na Nota Fiscal, impossibilitando a validação da carga. Além disso, foram identificadas datas de fabricação divergentes entre o produto físico e o faturado. Tais falhas impossibilitam o recebimento imediato, uma vez que comprometem o controle de qualidade e o padrão de conformidade Nitro.</t>
+  </si>
+  <si>
+    <t>12 caixas sujas e 08 molhadas</t>
+  </si>
+  <si>
+    <t>01 sacaria avariada</t>
+  </si>
+  <si>
+    <t>rnc-03-D</t>
+  </si>
+  <si>
+    <t>04006</t>
+  </si>
+  <si>
+    <t>MOLY 12 N+ CX02X05L</t>
+  </si>
+  <si>
+    <t>DEVOLUÇÃO CLIENTE</t>
+  </si>
+  <si>
+    <t>63950/24</t>
+  </si>
+  <si>
+    <t>04447</t>
+  </si>
+  <si>
+    <t>SULFATO DE ZINCO MONO RVI-F SCX25KG</t>
+  </si>
+  <si>
+    <t>YDP2025198913</t>
+  </si>
+  <si>
+    <t>DEVOLUÇÃO</t>
+  </si>
+  <si>
+    <t>Durante a descarga da devolução proveniente do cliente Alexsander Rudimar Borghetti, realizada pela transportadora Transouza, foi identificada a seguinte não conformidade: 
+A) O produto MOLY 12 N+ CX02X05L (NF 10712, Lote 63950/24) apresentou avarias em suas embalagens secundárias, totalizando 200L envolvidos. No momento da conferência, constataram-se 12 caixas sujas e 08 caixas molhadas. Tal condição caracteriza a descaracterização do padrão Nitro de apresentação e integridade, sendo necessária a ressalva para fins de recondicionamento ou bloqueio do lote.
+B) O produto MOLY 12 N+ CX02X05L (NF 10712, Lote YDP2025198913) apresentou 25kg avariados. No momento da conferência física, constatou-se 01 (uma) unidade de sacaria avariada, resultando na perda da integridade da embalagem e do conteúdo original. O material será segregado para os devidos procedimentos de qualidade.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,9 +417,16 @@
     </font>
     <font>
       <b/>
-      <u/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -390,7 +465,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.499984740745262"/>
+        <fgColor theme="8" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -456,14 +531,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -473,25 +540,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="13" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -500,6 +548,44 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -792,653 +878,413 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="19.95" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="21" width="25.77734375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="25.77734375" style="1" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="0" hidden="1" customWidth="1"/>
-    <col min="24" max="16384" width="8.88671875" style="1" hidden="1"/>
+    <col min="22" max="22" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="24" max="16384" width="25.77734375" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="22" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="19" t="s">
+    <row r="1" spans="1:23" s="15" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="20" t="s">
+      <c r="C1" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="O1" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="L1" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="R1" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="20" t="s">
+      <c r="S1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="20" t="s">
+      <c r="T1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="U1" s="20" t="s">
+      <c r="U1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="V1" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="W1" s="21"/>
+      <c r="W1" s="14"/>
     </row>
     <row r="2" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="16">
+        <v>357</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="16">
-        <v>356</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="F2" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="G2" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I2" s="18">
+        <v>5009</v>
+      </c>
+      <c r="J2" s="19">
+        <v>45602</v>
+      </c>
+      <c r="K2" s="19">
+        <v>46249</v>
+      </c>
+      <c r="L2" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="M2" s="19">
+        <v>45519</v>
+      </c>
+      <c r="N2" s="19">
+        <v>46249</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="20">
+        <v>210</v>
+      </c>
+      <c r="Q2" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="R2" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="10">
-        <v>10817</v>
-      </c>
-      <c r="J2" s="11">
-        <v>45842</v>
-      </c>
-      <c r="K2" s="11">
-        <v>46938</v>
-      </c>
-      <c r="L2" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="M2" s="11">
-        <v>45842</v>
-      </c>
-      <c r="N2" s="11">
-        <v>46938</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="P2" s="18">
-        <v>9800</v>
-      </c>
-      <c r="Q2" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2" s="15" t="s">
+      <c r="V2" s="10" t="str">
+        <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>PROCESSO</v>
+      </c>
+      <c r="W2"/>
+    </row>
+    <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="T2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="U2" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="V2" s="12" t="str">
-        <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
+      <c r="B3" s="16">
+        <v>358</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="I3" s="18">
+        <v>10706</v>
+      </c>
+      <c r="J3" s="19">
+        <v>45556</v>
+      </c>
+      <c r="K3" s="19">
+        <v>2958465</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="19">
+        <v>46090</v>
+      </c>
+      <c r="N3" s="19">
+        <v>46821</v>
+      </c>
+      <c r="O3" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="P3" s="20">
+        <v>30000</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="T3" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="V3" s="10" t="str">
+        <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>PROCESSO</v>
+      </c>
+      <c r="W3"/>
+    </row>
+    <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="16">
+        <v>359</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="18">
+        <v>10712</v>
+      </c>
+      <c r="J4" s="19">
+        <v>45652</v>
+      </c>
+      <c r="K4" s="19">
+        <v>46382</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" s="19">
+        <v>45652</v>
+      </c>
+      <c r="N4" s="19">
+        <v>46382</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="P4" s="20">
+        <v>200</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="T4" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="U4" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="10" t="str">
+        <f>IF(B4="",0,VLOOKUP(T4,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v xml:space="preserve">EMBALAGEM </v>
       </c>
-      <c r="W2"/>
-    </row>
-    <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="18"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="15"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="12">
-        <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W3"/>
-    </row>
-    <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="12">
-        <f>IF(B4="",0,VLOOKUP(T4,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
       <c r="W4"/>
     </row>
-    <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="10"/>
-      <c r="R5" s="10"/>
-      <c r="S5" s="15"/>
-      <c r="T5" s="10"/>
-      <c r="U5" s="10"/>
-      <c r="V5" s="12">
+    <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="16">
+        <v>359</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I5" s="18">
+        <v>10712</v>
+      </c>
+      <c r="J5" s="19">
+        <v>45853</v>
+      </c>
+      <c r="K5" s="19">
+        <v>46582</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="M5" s="19">
+        <v>45853</v>
+      </c>
+      <c r="N5" s="19">
+        <v>46582</v>
+      </c>
+      <c r="O5" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="P5" s="20">
+        <v>25</v>
+      </c>
+      <c r="Q5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="R5" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="S5" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="T5" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="U5" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="V5" s="10" t="str">
         <f>IF(B5="",0,VLOOKUP(T5,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
+        <v>AVARIA</v>
       </c>
       <c r="W5"/>
     </row>
-    <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16"/>
       <c r="B6" s="16"/>
       <c r="C6" s="16"/>
       <c r="D6" s="17"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
       <c r="O6" s="17"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="15"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="12">
+      <c r="P6" s="20"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="21"/>
+      <c r="T6" s="18"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="10">
         <f>IF(B6="",0,VLOOKUP(T6,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W6"/>
     </row>
-    <row r="7" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="12">
-        <f>IF(B7="",0,VLOOKUP(T7,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W7"/>
-    </row>
-    <row r="8" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="12">
-        <f>IF(B8="",0,VLOOKUP(T8,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W8"/>
-    </row>
-    <row r="9" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="12">
-        <f>IF(B9="",0,VLOOKUP(T9,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W9"/>
-    </row>
-    <row r="10" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="18"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="12">
-        <f>IF(B10="",0,VLOOKUP(T10,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W10"/>
-    </row>
-    <row r="11" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="12">
-        <f>IF(B11="",0,VLOOKUP(T11,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W11"/>
-    </row>
-    <row r="12" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="12">
-        <f>IF(B12="",0,VLOOKUP(T12,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W12"/>
-    </row>
-    <row r="13" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="12">
-        <f>IF(B13="",0,VLOOKUP(T13,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W13"/>
-    </row>
-    <row r="14" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="12">
-        <f>IF(B14="",0,VLOOKUP(T14,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W14"/>
-    </row>
-    <row r="15" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="12">
-        <f>IF(B15="",0,VLOOKUP(T15,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W15"/>
-    </row>
-    <row r="16" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="12">
-        <f>IF(B16="",0,VLOOKUP(T16,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W16"/>
-    </row>
-    <row r="17" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="12">
-        <f>IF(B17="",0,VLOOKUP(T17,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W17"/>
-    </row>
-    <row r="18" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="12">
-        <f>IF(B18="",0,VLOOKUP(T18,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W18"/>
-    </row>
-    <row r="19" spans="1:23" s="9" customFormat="1" ht="19.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="12">
-        <f>IF(B19="",0,VLOOKUP(T19,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
-      </c>
-      <c r="W19"/>
-    </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q19" xr:uid="{AEBEAE45-30D1-4542-A1D6-EBC88D16BDC1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6" xr:uid="{AEBEAE45-30D1-4542-A1D6-EBC88D16BDC1}">
       <formula1>"KG, L, Ds"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:V19" xr:uid="{515AD032-001C-4B14-8366-B098E8D106E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:V6" xr:uid="{515AD032-001C-4B14-8366-B098E8D106E9}">
       <formula1>"NITRO, FORNECEDOR, DEVOLUÇÃO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R19" xr:uid="{9224D280-D2F8-4702-BD9E-3A2E00F78617}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R6" xr:uid="{9224D280-D2F8-4702-BD9E-3A2E00F78617}">
       <formula1>"Saco, Bombona, Palete, Caixa, Big Bag, Galão"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G19" xr:uid="{0CCEE7D2-5A92-4296-95B7-680EA05B05B1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G6" xr:uid="{0CCEE7D2-5A92-4296-95B7-680EA05B05B1}">
       <formula1>"VZP TRANSF HORT, DEVOLUÇÃO CLIENTE, VZP TRANSF CBA, RECEBIMENTO PORTO, ROO TRANSF HORT, ROO TRANSF CBA, HORT TRANSF CBA, TORRE DE CONTROLE, TRANSP. RODOFROTA, STZ TRANSF HORT, CBA TRANSF HORT, STZ TRANSF CBA, FORNECEDOR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E19 G2:G19" xr:uid="{A9DDEBF6-CC05-4C4C-B66F-05CC7D4CAF45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 G2:G6" xr:uid="{A9DDEBF6-CC05-4C4C-B66F-05CC7D4CAF45}">
       <formula1>"Cuiabá, Hortolândia"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H19" xr:uid="{EE69AD02-7E08-441A-857C-3BD9A1515FF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H6" xr:uid="{EE69AD02-7E08-441A-857C-3BD9A1515FF8}">
       <formula1>"FORNECEDOR, DEVOLUÇÃO CLIENTE, VZP NITRO, HORT, CUIABÁ"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1452,7 +1298,7 @@
           <x14:formula1>
             <xm:f>Planilha1!$A$2:$A$14</xm:f>
           </x14:formula1>
-          <xm:sqref>T2:T19</xm:sqref>
+          <xm:sqref>T2:T6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1476,9 +1322,9 @@
         <v>30</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1486,7 +1332,7 @@
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="6"/>
@@ -1495,56 +1341,56 @@
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="14"/>
+        <v>34</v>
+      </c>
+      <c r="F3" s="12"/>
     </row>
     <row r="4" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>42</v>
+      <c r="B4" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>42</v>
+      <c r="B5" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>42</v>
+      <c r="B6" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>42</v>
+      <c r="B7" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7"/>
     </row>
@@ -1552,11 +1398,11 @@
       <c r="A8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8"/>
     </row>
@@ -1564,7 +1410,7 @@
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D9"/>
@@ -1574,7 +1420,7 @@
       <c r="A10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D10"/>
@@ -1584,7 +1430,7 @@
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D11"/>
@@ -1594,7 +1440,7 @@
       <c r="A12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="12" t="s">
         <v>27</v>
       </c>
       <c r="D12"/>
@@ -1604,7 +1450,7 @@
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D13"/>
@@ -1614,7 +1460,7 @@
       <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D14"/>

--- a/Plan_RNC.xlsx
+++ b/Plan_RNC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\RNC-RA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B667EE4E-1C3E-4B6C-8AF5-93F925068D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6838D76-F330-4171-B4F6-631EDE757737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>NUMERO-NF</t>
   </si>
@@ -207,9 +207,6 @@
     <t>RESUMO-RAPIDO</t>
   </si>
   <si>
-    <t>DATA FABRICAÇÃO DIVERGENTE</t>
-  </si>
-  <si>
     <t>rnc-01</t>
   </si>
   <si>
@@ -234,21 +231,9 @@
     <t>NITRO</t>
   </si>
   <si>
-    <t>Durante a descarga da transferência proveniente da unidade de Cuiabá para Hortolândia, realizada pela transportadora Fantinato, veículo placa SUF2B15, foi identificada a seguinte não conformidade: A) O produto NITRO 25-01 CX02X05L (NF 5009, Lote 002-24) apresentou divergência na informação de data de fabricação, totalizando 210L envolvidos na movimentação. No momento da conferência física, constatou-se que a data gravada nas embalagens não condiz com o informado no documento fiscal, comprometendo a rastreabilidade do lote e o padrão de conformidade Nitro.</t>
-  </si>
-  <si>
-    <t>DATAS DIVERGENTES E LOTE NÃO CONSTA NA NF</t>
-  </si>
-  <si>
     <t>rnc-02</t>
   </si>
   <si>
-    <t>00104</t>
-  </si>
-  <si>
-    <t>SPEED GRAMINEA SCX25KG</t>
-  </si>
-  <si>
     <t>VZP TRANSF HORT</t>
   </si>
   <si>
@@ -258,54 +243,100 @@
     <t>VZP NITRO</t>
   </si>
   <si>
-    <t>Lote WMS</t>
-  </si>
-  <si>
-    <t>75355/26</t>
-  </si>
-  <si>
     <t>KG</t>
   </si>
   <si>
-    <t>Durante recebimento proveniente da unidade de VZP para Hortolândia, realizado pela transportadora MMCM, veículo placa EF08D60, foram identificadas inconformidades na documentação fiscal: A) O produto SPEED GRAMINEA SCX25KG (NF 10706), totalizando 30.000kg, apresentou divergência crítica de rastreabilidade. No momento da conferência física, constatou-se que a informação de Lote não consta na Nota Fiscal, impossibilitando a validação da carga. Além disso, foram identificadas datas de fabricação divergentes entre o produto físico e o faturado. Tais falhas impossibilitam o recebimento imediato, uma vez que comprometem o controle de qualidade e o padrão de conformidade Nitro.</t>
-  </si>
-  <si>
-    <t>12 caixas sujas e 08 molhadas</t>
-  </si>
-  <si>
-    <t>01 sacaria avariada</t>
-  </si>
-  <si>
-    <t>rnc-03-D</t>
-  </si>
-  <si>
-    <t>04006</t>
-  </si>
-  <si>
-    <t>MOLY 12 N+ CX02X05L</t>
-  </si>
-  <si>
     <t>DEVOLUÇÃO CLIENTE</t>
   </si>
   <si>
-    <t>63950/24</t>
-  </si>
-  <si>
-    <t>04447</t>
-  </si>
-  <si>
-    <t>SULFATO DE ZINCO MONO RVI-F SCX25KG</t>
-  </si>
-  <si>
-    <t>YDP2025198913</t>
-  </si>
-  <si>
     <t>DEVOLUÇÃO</t>
   </si>
   <si>
-    <t>Durante a descarga da devolução proveniente do cliente Alexsander Rudimar Borghetti, realizada pela transportadora Transouza, foi identificada a seguinte não conformidade: 
-A) O produto MOLY 12 N+ CX02X05L (NF 10712, Lote 63950/24) apresentou avarias em suas embalagens secundárias, totalizando 200L envolvidos. No momento da conferência, constataram-se 12 caixas sujas e 08 caixas molhadas. Tal condição caracteriza a descaracterização do padrão Nitro de apresentação e integridade, sendo necessária a ressalva para fins de recondicionamento ou bloqueio do lote.
-B) O produto MOLY 12 N+ CX02X05L (NF 10712, Lote YDP2025198913) apresentou 25kg avariados. No momento da conferência física, constatou-se 01 (uma) unidade de sacaria avariada, resultando na perda da integridade da embalagem e do conteúdo original. O material será segregado para os devidos procedimentos de qualidade.</t>
+    <t>rnc-03</t>
+  </si>
+  <si>
+    <t>rnc-04</t>
+  </si>
+  <si>
+    <t>rnc-05</t>
+  </si>
+  <si>
+    <t>rnc-06</t>
+  </si>
+  <si>
+    <t>DATA DE FABRICAÇÃO DIVERGENTE</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>Durante o recebimento da transferência CBA / Hortolândia realizado pela transportadora FANTINATO, veículo placa SUF2B15, foi identificada a seguinte não conformidade: A) O produto NITRO 25-01 CX02X05L (NF 5009, Lote 002-24) apresentou divergência na informação de data de fabricação, totalizando 210L envolvidos. No momento da conferência física, constatou-se que a data gravada nas embalagens não condiz com o informado no documento fiscal, comprometendo a rastreabilidade do lote e o padrão de conformidade Nitro.</t>
+  </si>
+  <si>
+    <t>EMBALAGEM AVARIADA, MOLHADA E SUJA</t>
+  </si>
+  <si>
+    <t>04170</t>
+  </si>
+  <si>
+    <t>GROWN 1000L</t>
+  </si>
+  <si>
+    <t>VZP TRANSF CBA</t>
+  </si>
+  <si>
+    <t>75490/26</t>
+  </si>
+  <si>
+    <t>Durante o processo de recebimento da transferência VZP → CBA, realizado pela transportadora Fantinato, veículo placa EJZ3B01, foi identificada a seguinte não conformidade: A) O produto GROWN 1000L (IBC) apresentou avaria crítica na embalagem primária. No momento da descarga, constatou-se que 01 IBC estava com um furo e apresentava sujidade, resultando em vazamento de produto e comprometendo o padrão de integridade e segurança da carga. O volume de 1000L foi segregado para análise de perda e procedimentos de contenção.</t>
+  </si>
+  <si>
+    <t>LOTE DA ETIQUETA DIVERGENTE</t>
+  </si>
+  <si>
+    <t>510009</t>
+  </si>
+  <si>
+    <t>BOROMAG CX02X10KG</t>
+  </si>
+  <si>
+    <t>70809/25</t>
+  </si>
+  <si>
+    <t>Durante o processo de recebimento da transferência VZP → Hortolândia, proveniente da transportadora MMCM, veículo placa GBL7F73, foi identificada uma inconsistência grave de rastreabilidade: A) O produto BOROMAG CX02X10KG (NF 10792), totalizando 16.800kg, apresentou divergência tripla de lote. Constatou-se que o lote informado na etiqueta individual do produto não coincide com o lote impresso na caixa (embalagem secundária), e ambos divergem do lote declarado na Nota Fiscal (Lote 70809/25). Essa falha compromete totalmente a garantia de origem e a rastreabilidade do material, impossibilitando o recebimento nos padrões de qualidade Nitro.</t>
+  </si>
+  <si>
+    <t>RIZOPLANT - AZOS 2 - CX120DS</t>
+  </si>
+  <si>
+    <t>540067</t>
+  </si>
+  <si>
+    <t>005648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durante a descarga da devolução, foi identificada a seguinte movimentação: A) O produto RIZOPLANT - AZOS 2 - CX120DS (NF 10968, Lote 005648), totalizando 120DS (5.760kg), foi recebido na unidade. O volume passará pelos procedimentos de conferência física e documental para validação da integridade das embalagens e posterior reingresso ao estoque ou destinação conforme política de devoluções. </t>
+  </si>
+  <si>
+    <t>Durante o processo de recebimento proveniente da transferência VZP → Hortolândia, transportadora MMCM, veículo placa BYP3915, foi identificada uma inconsistência crítica de rastreabilidade, similar a ocorrências anteriores: A) O produto BOROMAG CX02X10KG (NF 10795), totalizando 14.000kg, apresentou divergência de lote entre os níveis de embalagem. No momento da conferência, constatou-se que a etiqueta individual do produto indica o Lote 510009, enquanto a caixa (embalagem secundária) e a Nota Fiscal indicam o Lote 70809/25. Esta desconformidade impossibilita a garantia da rastreabilidade plena do material e fere os protocolos de recebimento da Nitro.</t>
+  </si>
+  <si>
+    <t>EMBALAGEM AVARIADA COM VAZAMENTO</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>OCTABORATO DE SODIO SCX25KG</t>
+  </si>
+  <si>
+    <t>0647/25</t>
+  </si>
+  <si>
+    <t>Acerca da devolução, foi identificada a seguinte não conformidade: A) O produto OCTABORATO DE SODIO SCX25KG (NF 1237, Lote 0647/25) apresentou avaria crítica em múltiplas unidades, totalizando 300kg afetados. No ato do recebimento, constatou-se que 12 sacarias estavam rompidas, apresentando vazamento do conteúdo. A carga foi segregada imediatamente para evitar contaminação de outros lotes e para os procedimentos de pesagem e bloqueio.</t>
+  </si>
+  <si>
+    <t>70809/26</t>
   </si>
 </sst>
 </file>
@@ -459,13 +490,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.499984740745262"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -540,18 +571,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -573,19 +600,34 @@
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -878,76 +920,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="19.95" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="21" width="25.77734375" style="1" customWidth="1"/>
-    <col min="22" max="22" width="0" style="1" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="25.77734375" style="1" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="25.77734375" hidden="1" customWidth="1"/>
     <col min="24" max="16384" width="25.77734375" style="1" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="15" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="O1" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="23" t="s">
+      <c r="P1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="Q1" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="23" t="s">
+      <c r="R1" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="S1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="23" t="s">
+      <c r="T1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="U1" s="23" t="s">
+      <c r="U1" s="22" t="s">
         <v>32</v>
       </c>
       <c r="V1" s="13" t="s">
@@ -956,68 +999,68 @@
       <c r="W1" s="14"/>
     </row>
     <row r="2" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="17">
+        <v>360</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="16">
-        <v>357</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="D2" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="H2" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="17">
+        <v>5009</v>
+      </c>
+      <c r="J2" s="18">
+        <v>45602</v>
+      </c>
+      <c r="K2" s="18">
+        <v>46249</v>
+      </c>
+      <c r="L2" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="18">
-        <v>5009</v>
-      </c>
-      <c r="J2" s="19">
-        <v>45602</v>
-      </c>
-      <c r="K2" s="19">
+      <c r="M2" s="18">
+        <v>45519</v>
+      </c>
+      <c r="N2" s="18">
         <v>46249</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="O2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="19">
+        <v>210</v>
+      </c>
+      <c r="Q2" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="M2" s="19">
-        <v>45519</v>
-      </c>
-      <c r="N2" s="19">
-        <v>46249</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="P2" s="20">
-        <v>210</v>
-      </c>
-      <c r="Q2" s="18" t="s">
+      <c r="R2" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="17" t="s">
         <v>55</v>
-      </c>
-      <c r="R2" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="T2" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="U2" s="18" t="s">
-        <v>56</v>
       </c>
       <c r="V2" s="10" t="str">
         <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
@@ -1026,265 +1069,539 @@
       <c r="W2"/>
     </row>
     <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="16">
-        <v>358</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="A3" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="17">
+        <v>361</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="18">
-        <v>10706</v>
-      </c>
-      <c r="J3" s="19">
-        <v>45556</v>
-      </c>
-      <c r="K3" s="19">
-        <v>2958465</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="M3" s="19">
-        <v>46090</v>
-      </c>
-      <c r="N3" s="19">
-        <v>46821</v>
-      </c>
-      <c r="O3" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="P3" s="20">
-        <v>30000</v>
-      </c>
-      <c r="Q3" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="R3" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="T3" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="18" t="s">
-        <v>56</v>
+      <c r="I3" s="17">
+        <v>10786</v>
+      </c>
+      <c r="J3" s="18">
+        <v>46100</v>
+      </c>
+      <c r="K3" s="18">
+        <v>47196</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M3" s="18">
+        <v>46100</v>
+      </c>
+      <c r="N3" s="18">
+        <v>47196</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="P3" s="19">
+        <v>1000</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="S3" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="T3" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="U3" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="V3" s="10" t="str">
         <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
+        <v>AVARIA</v>
       </c>
       <c r="W3"/>
     </row>
     <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="16">
-        <v>359</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="18">
-        <v>10712</v>
-      </c>
-      <c r="J4" s="19">
-        <v>45652</v>
-      </c>
-      <c r="K4" s="19">
-        <v>46382</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="M4" s="19">
-        <v>45652</v>
-      </c>
-      <c r="N4" s="19">
-        <v>46382</v>
-      </c>
-      <c r="O4" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="P4" s="20">
-        <v>200</v>
-      </c>
-      <c r="Q4" s="18" t="s">
+      <c r="A4" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="17">
+        <v>362</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="17">
+        <v>10792</v>
+      </c>
+      <c r="J4" s="18">
+        <v>45901</v>
+      </c>
+      <c r="K4" s="18">
+        <v>46997</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="M4" s="18">
+        <v>45901</v>
+      </c>
+      <c r="N4" s="18">
+        <v>46997</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="P4" s="19">
+        <v>16800</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" s="17" t="s">
         <v>55</v>
-      </c>
-      <c r="R4" s="18" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="T4" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="U4" s="25" t="s">
-        <v>79</v>
       </c>
       <c r="V4" s="10" t="str">
         <f>IF(B4="",0,VLOOKUP(T4,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v xml:space="preserve">EMBALAGEM </v>
+        <v>PROCESSO</v>
       </c>
       <c r="W4"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="16">
-        <v>359</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" s="18">
-        <v>10712</v>
-      </c>
-      <c r="J5" s="19">
-        <v>45853</v>
-      </c>
-      <c r="K5" s="19">
-        <v>46582</v>
-      </c>
-      <c r="L5" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M5" s="19">
-        <v>45853</v>
-      </c>
-      <c r="N5" s="19">
-        <v>46582</v>
-      </c>
-      <c r="O5" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="P5" s="20">
-        <v>25</v>
-      </c>
-      <c r="Q5" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="R5" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="T5" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="U5" s="25" t="s">
-        <v>79</v>
+      <c r="A5" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="17">
+        <v>363</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="17">
+        <v>10968</v>
+      </c>
+      <c r="J5" s="18">
+        <v>45863</v>
+      </c>
+      <c r="K5" s="18">
+        <v>46137</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="M5" s="18">
+        <v>45863</v>
+      </c>
+      <c r="N5" s="18">
+        <v>46137</v>
+      </c>
+      <c r="O5" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="P5" s="19">
+        <v>5760</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="R5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="T5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="U5" s="17" t="s">
+        <v>62</v>
       </c>
       <c r="V5" s="10" t="str">
         <f>IF(B5="",0,VLOOKUP(T5,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>PROCESSO</v>
+      </c>
+      <c r="W5"/>
+    </row>
+    <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="23">
+        <v>364</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="23">
+        <v>10795</v>
+      </c>
+      <c r="J6" s="25">
+        <v>45901</v>
+      </c>
+      <c r="K6" s="25">
+        <v>46997</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="M6" s="25">
+        <v>45901</v>
+      </c>
+      <c r="N6" s="25">
+        <v>46997</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="P6" s="26">
+        <v>14000</v>
+      </c>
+      <c r="Q6" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="R6" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="S6" s="27" t="s">
+        <v>85</v>
+      </c>
+      <c r="T6" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="U6" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="V6" s="28" t="str">
+        <f>IF(B6="",0,VLOOKUP(T6,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>PROCESSO</v>
+      </c>
+      <c r="W6"/>
+    </row>
+    <row r="7" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="23">
+        <v>365</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="23">
+        <v>1237</v>
+      </c>
+      <c r="J7" s="25">
+        <v>45819</v>
+      </c>
+      <c r="K7" s="25">
+        <v>46549</v>
+      </c>
+      <c r="L7" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="M7" s="25">
+        <v>45819</v>
+      </c>
+      <c r="N7" s="25">
+        <v>46549</v>
+      </c>
+      <c r="O7" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="P7" s="26">
+        <v>300</v>
+      </c>
+      <c r="Q7" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="S7" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="T7" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="U7" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="V7" s="28" t="str">
+        <f>IF(B7="",0,VLOOKUP(T7,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>AVARIA</v>
       </c>
-      <c r="W5"/>
-    </row>
-    <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="21"/>
-      <c r="T6" s="18"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="10">
-        <f>IF(B6="",0,VLOOKUP(T6,Planilha1!$A$2:$B$14,2,FALSE))</f>
+    </row>
+    <row r="8" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="27"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="28">
+        <f>IF(B8="",0,VLOOKUP(T8,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="W6"/>
+    </row>
+    <row r="9" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="27"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="28">
+        <f>IF(B9="",0,VLOOKUP(T9,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="10">
+        <f>IF(B10="",0,VLOOKUP(T10,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="17"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="17"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="10">
+        <f>IF(B11="",0,VLOOKUP(T11,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="10">
+        <f>IF(B12="",0,VLOOKUP(T12,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="10">
+        <f>IF(B13="",0,VLOOKUP(T13,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q6" xr:uid="{AEBEAE45-30D1-4542-A1D6-EBC88D16BDC1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q13" xr:uid="{AEBEAE45-30D1-4542-A1D6-EBC88D16BDC1}">
       <formula1>"KG, L, Ds"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:V6" xr:uid="{515AD032-001C-4B14-8366-B098E8D106E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:V13" xr:uid="{515AD032-001C-4B14-8366-B098E8D106E9}">
       <formula1>"NITRO, FORNECEDOR, DEVOLUÇÃO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R6" xr:uid="{9224D280-D2F8-4702-BD9E-3A2E00F78617}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R13" xr:uid="{9224D280-D2F8-4702-BD9E-3A2E00F78617}">
       <formula1>"Saco, Bombona, Palete, Caixa, Big Bag, Galão"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G6" xr:uid="{0CCEE7D2-5A92-4296-95B7-680EA05B05B1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G13" xr:uid="{0CCEE7D2-5A92-4296-95B7-680EA05B05B1}">
       <formula1>"VZP TRANSF HORT, DEVOLUÇÃO CLIENTE, VZP TRANSF CBA, RECEBIMENTO PORTO, ROO TRANSF HORT, ROO TRANSF CBA, HORT TRANSF CBA, TORRE DE CONTROLE, TRANSP. RODOFROTA, STZ TRANSF HORT, CBA TRANSF HORT, STZ TRANSF CBA, FORNECEDOR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6 G2:G6" xr:uid="{A9DDEBF6-CC05-4C4C-B66F-05CC7D4CAF45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G13 E2:E13" xr:uid="{A9DDEBF6-CC05-4C4C-B66F-05CC7D4CAF45}">
       <formula1>"Cuiabá, Hortolândia"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H6" xr:uid="{EE69AD02-7E08-441A-857C-3BD9A1515FF8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H13" xr:uid="{EE69AD02-7E08-441A-857C-3BD9A1515FF8}">
       <formula1>"FORNECEDOR, DEVOLUÇÃO CLIENTE, VZP NITRO, HORT, CUIABÁ"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1298,7 +1615,7 @@
           <x14:formula1>
             <xm:f>Planilha1!$A$2:$A$14</xm:f>
           </x14:formula1>
-          <xm:sqref>T2:T6</xm:sqref>
+          <xm:sqref>T2:T13</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Plan_RNC.xlsx
+++ b/Plan_RNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\RNC-RA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6838D76-F330-4171-B4F6-631EDE757737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976FC62D-F473-42EC-ACD9-B3D280A007AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="69">
   <si>
     <t>NUMERO-NF</t>
   </si>
@@ -207,136 +207,67 @@
     <t>RESUMO-RAPIDO</t>
   </si>
   <si>
-    <t>rnc-01</t>
-  </si>
-  <si>
-    <t>05272</t>
+    <t>RNC-01</t>
   </si>
   <si>
     <t>Hortolândia</t>
   </si>
   <si>
-    <t>NITRO 25-01 CX02X05L</t>
-  </si>
-  <si>
-    <t>CBA TRANSF HORT</t>
-  </si>
-  <si>
-    <t>002-24</t>
+    <t>VZP TRANSF HORT</t>
+  </si>
+  <si>
+    <t>VZP NITRO</t>
+  </si>
+  <si>
+    <t>NITRO</t>
+  </si>
+  <si>
+    <t>UM GALÃO DE 5L COM VAZAMENTO</t>
+  </si>
+  <si>
+    <t>CAIXAS AMASSADAS, RASGADAS E DOIS GALÕES DE 10L COM VAZAMENTO</t>
+  </si>
+  <si>
+    <t>CAIXAS AMASSADAS E UM GALÃO DE 5L COM VAZAMENTO</t>
+  </si>
+  <si>
+    <t>DATA DE VALIDADE DIVERTE DA NF</t>
+  </si>
+  <si>
+    <t>1000041</t>
+  </si>
+  <si>
+    <t>05043</t>
+  </si>
+  <si>
+    <t>510052</t>
+  </si>
+  <si>
+    <t>ELMO CX02X05L</t>
+  </si>
+  <si>
+    <t>DUNNA CX02X05L</t>
+  </si>
+  <si>
+    <t>ARRANK CX02X05L</t>
+  </si>
+  <si>
+    <t>FB1324</t>
+  </si>
+  <si>
+    <t>FB1125</t>
+  </si>
+  <si>
+    <t>SKB0324.B</t>
+  </si>
+  <si>
+    <t>74604/26</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>NITRO</t>
-  </si>
-  <si>
-    <t>rnc-02</t>
-  </si>
-  <si>
-    <t>VZP TRANSF HORT</t>
-  </si>
-  <si>
-    <t>CUIABÁ</t>
-  </si>
-  <si>
-    <t>VZP NITRO</t>
-  </si>
-  <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>DEVOLUÇÃO CLIENTE</t>
-  </si>
-  <si>
-    <t>DEVOLUÇÃO</t>
-  </si>
-  <si>
-    <t>rnc-03</t>
-  </si>
-  <si>
-    <t>rnc-04</t>
-  </si>
-  <si>
-    <t>rnc-05</t>
-  </si>
-  <si>
-    <t>rnc-06</t>
-  </si>
-  <si>
-    <t>DATA DE FABRICAÇÃO DIVERGENTE</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>Durante o recebimento da transferência CBA / Hortolândia realizado pela transportadora FANTINATO, veículo placa SUF2B15, foi identificada a seguinte não conformidade: A) O produto NITRO 25-01 CX02X05L (NF 5009, Lote 002-24) apresentou divergência na informação de data de fabricação, totalizando 210L envolvidos. No momento da conferência física, constatou-se que a data gravada nas embalagens não condiz com o informado no documento fiscal, comprometendo a rastreabilidade do lote e o padrão de conformidade Nitro.</t>
-  </si>
-  <si>
-    <t>EMBALAGEM AVARIADA, MOLHADA E SUJA</t>
-  </si>
-  <si>
-    <t>04170</t>
-  </si>
-  <si>
-    <t>GROWN 1000L</t>
-  </si>
-  <si>
-    <t>VZP TRANSF CBA</t>
-  </si>
-  <si>
-    <t>75490/26</t>
-  </si>
-  <si>
-    <t>Durante o processo de recebimento da transferência VZP → CBA, realizado pela transportadora Fantinato, veículo placa EJZ3B01, foi identificada a seguinte não conformidade: A) O produto GROWN 1000L (IBC) apresentou avaria crítica na embalagem primária. No momento da descarga, constatou-se que 01 IBC estava com um furo e apresentava sujidade, resultando em vazamento de produto e comprometendo o padrão de integridade e segurança da carga. O volume de 1000L foi segregado para análise de perda e procedimentos de contenção.</t>
-  </si>
-  <si>
-    <t>LOTE DA ETIQUETA DIVERGENTE</t>
-  </si>
-  <si>
-    <t>510009</t>
-  </si>
-  <si>
-    <t>BOROMAG CX02X10KG</t>
-  </si>
-  <si>
-    <t>70809/25</t>
-  </si>
-  <si>
-    <t>Durante o processo de recebimento da transferência VZP → Hortolândia, proveniente da transportadora MMCM, veículo placa GBL7F73, foi identificada uma inconsistência grave de rastreabilidade: A) O produto BOROMAG CX02X10KG (NF 10792), totalizando 16.800kg, apresentou divergência tripla de lote. Constatou-se que o lote informado na etiqueta individual do produto não coincide com o lote impresso na caixa (embalagem secundária), e ambos divergem do lote declarado na Nota Fiscal (Lote 70809/25). Essa falha compromete totalmente a garantia de origem e a rastreabilidade do material, impossibilitando o recebimento nos padrões de qualidade Nitro.</t>
-  </si>
-  <si>
-    <t>RIZOPLANT - AZOS 2 - CX120DS</t>
-  </si>
-  <si>
-    <t>540067</t>
-  </si>
-  <si>
-    <t>005648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durante a descarga da devolução, foi identificada a seguinte movimentação: A) O produto RIZOPLANT - AZOS 2 - CX120DS (NF 10968, Lote 005648), totalizando 120DS (5.760kg), foi recebido na unidade. O volume passará pelos procedimentos de conferência física e documental para validação da integridade das embalagens e posterior reingresso ao estoque ou destinação conforme política de devoluções. </t>
-  </si>
-  <si>
-    <t>Durante o processo de recebimento proveniente da transferência VZP → Hortolândia, transportadora MMCM, veículo placa BYP3915, foi identificada uma inconsistência crítica de rastreabilidade, similar a ocorrências anteriores: A) O produto BOROMAG CX02X10KG (NF 10795), totalizando 14.000kg, apresentou divergência de lote entre os níveis de embalagem. No momento da conferência, constatou-se que a etiqueta individual do produto indica o Lote 510009, enquanto a caixa (embalagem secundária) e a Nota Fiscal indicam o Lote 70809/25. Esta desconformidade impossibilita a garantia da rastreabilidade plena do material e fere os protocolos de recebimento da Nitro.</t>
-  </si>
-  <si>
-    <t>EMBALAGEM AVARIADA COM VAZAMENTO</t>
-  </si>
-  <si>
-    <t>63</t>
-  </si>
-  <si>
-    <t>OCTABORATO DE SODIO SCX25KG</t>
-  </si>
-  <si>
-    <t>0647/25</t>
-  </si>
-  <si>
-    <t>Acerca da devolução, foi identificada a seguinte não conformidade: A) O produto OCTABORATO DE SODIO SCX25KG (NF 1237, Lote 0647/25) apresentou avaria crítica em múltiplas unidades, totalizando 300kg afetados. No ato do recebimento, constatou-se que 12 sacarias estavam rompidas, apresentando vazamento do conteúdo. A carga foi segregada imediatamente para evitar contaminação de outros lotes e para os procedimentos de pesagem e bloqueio.</t>
-  </si>
-  <si>
-    <t>70809/26</t>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -1000,137 +931,137 @@
     </row>
     <row r="2" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B2" s="17">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D2" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="H2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>58</v>
-      </c>
       <c r="I2" s="17">
-        <v>5009</v>
+        <v>10778</v>
       </c>
       <c r="J2" s="18">
-        <v>45602</v>
+        <v>45551</v>
       </c>
       <c r="K2" s="18">
-        <v>46249</v>
+        <v>46108</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="M2" s="18">
-        <v>45519</v>
+        <v>45551</v>
       </c>
       <c r="N2" s="18">
-        <v>46249</v>
+        <v>46108</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="P2" s="19">
-        <v>210</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="17" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="R2" s="17" t="s">
         <v>37</v>
       </c>
       <c r="S2" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="V2" s="10" t="str">
         <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
+        <v>AVARIA</v>
       </c>
       <c r="W2"/>
     </row>
     <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B3" s="17">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E3" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="17">
+        <v>10778</v>
+      </c>
+      <c r="J3" s="18">
+        <v>45900</v>
+      </c>
+      <c r="K3" s="18">
+        <v>46446</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" s="18">
+        <v>45900</v>
+      </c>
+      <c r="N3" s="18">
+        <v>46446</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="P3" s="19">
+        <v>160</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S3" s="20" t="s">
         <v>68</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="17">
-        <v>10786</v>
-      </c>
-      <c r="J3" s="18">
-        <v>46100</v>
-      </c>
-      <c r="K3" s="18">
-        <v>47196</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="M3" s="18">
-        <v>46100</v>
-      </c>
-      <c r="N3" s="18">
-        <v>47196</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="P3" s="19">
-        <v>1000</v>
-      </c>
-      <c r="Q3" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="R3" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="S3" s="20" t="s">
-        <v>75</v>
       </c>
       <c r="T3" s="17" t="s">
         <v>11</v>
       </c>
       <c r="U3" s="17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="V3" s="10" t="str">
         <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
@@ -1140,137 +1071,137 @@
     </row>
     <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="B4" s="17">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="E4" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>57</v>
-      </c>
       <c r="H4" s="17" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I4" s="17">
-        <v>10792</v>
+        <v>10778</v>
       </c>
       <c r="J4" s="18">
-        <v>45901</v>
+        <v>45505</v>
       </c>
       <c r="K4" s="18">
-        <v>46997</v>
+        <v>46108</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="M4" s="18">
-        <v>45901</v>
+        <v>45505</v>
       </c>
       <c r="N4" s="18">
-        <v>46997</v>
+        <v>46108</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="P4" s="19">
-        <v>16800</v>
+        <v>115</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="R4" s="17" t="s">
         <v>37</v>
       </c>
       <c r="S4" s="20" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="V4" s="10" t="str">
         <f>IF(B4="",0,VLOOKUP(T4,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
+        <v xml:space="preserve">EMBALAGEM </v>
       </c>
       <c r="W4"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="17">
+        <v>366</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B5" s="17">
-        <v>363</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="G5" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>61</v>
-      </c>
       <c r="H5" s="17" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I5" s="17">
-        <v>10968</v>
+        <v>10778</v>
       </c>
       <c r="J5" s="18">
-        <v>45863</v>
+        <v>46090</v>
       </c>
       <c r="K5" s="18">
-        <v>46137</v>
+        <v>46821</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="M5" s="18">
-        <v>45863</v>
+        <v>46090</v>
       </c>
       <c r="N5" s="18">
-        <v>46137</v>
+        <v>47186</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="P5" s="19">
-        <v>5760</v>
+        <v>10800</v>
       </c>
       <c r="Q5" s="17" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="R5" s="17" t="s">
         <v>37</v>
       </c>
       <c r="S5" s="20" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U5" s="17" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="V5" s="10" t="str">
         <f>IF(B5="",0,VLOOKUP(T5,Planilha1!$A$2:$B$14,2,FALSE))</f>
@@ -1279,142 +1210,58 @@
       <c r="W5"/>
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="B6" s="23">
-        <v>364</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="23">
-        <v>10795</v>
-      </c>
-      <c r="J6" s="25">
-        <v>45901</v>
-      </c>
-      <c r="K6" s="25">
-        <v>46997</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="M6" s="25">
-        <v>45901</v>
-      </c>
-      <c r="N6" s="25">
-        <v>46997</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="P6" s="26">
-        <v>14000</v>
-      </c>
-      <c r="Q6" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="R6" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="S6" s="27" t="s">
-        <v>85</v>
-      </c>
-      <c r="T6" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="U6" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="V6" s="28" t="str">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="28">
         <f>IF(B6="",0,VLOOKUP(T6,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
+        <v>0</v>
       </c>
       <c r="W6"/>
     </row>
     <row r="7" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="23">
-        <v>365</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="23">
-        <v>1237</v>
-      </c>
-      <c r="J7" s="25">
-        <v>45819</v>
-      </c>
-      <c r="K7" s="25">
-        <v>46549</v>
-      </c>
-      <c r="L7" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="M7" s="25">
-        <v>45819</v>
-      </c>
-      <c r="N7" s="25">
-        <v>46549</v>
-      </c>
-      <c r="O7" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="P7" s="26">
-        <v>300</v>
-      </c>
-      <c r="Q7" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="R7" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="S7" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="T7" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="U7" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="V7" s="28" t="str">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="V7" s="28">
         <f>IF(B7="",0,VLOOKUP(T7,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>AVARIA</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">

--- a/Plan_RNC.xlsx
+++ b/Plan_RNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\RNC-RA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{976FC62D-F473-42EC-ACD9-B3D280A007AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48DC7E4-1854-4E14-B3DD-8E43EB314D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="69">
   <si>
     <t>NUMERO-NF</t>
   </si>
@@ -222,52 +222,52 @@
     <t>NITRO</t>
   </si>
   <si>
-    <t>UM GALÃO DE 5L COM VAZAMENTO</t>
-  </si>
-  <si>
-    <t>CAIXAS AMASSADAS, RASGADAS E DOIS GALÕES DE 10L COM VAZAMENTO</t>
-  </si>
-  <si>
-    <t>CAIXAS AMASSADAS E UM GALÃO DE 5L COM VAZAMENTO</t>
-  </si>
-  <si>
-    <t>DATA DE VALIDADE DIVERTE DA NF</t>
-  </si>
-  <si>
-    <t>1000041</t>
-  </si>
-  <si>
-    <t>05043</t>
-  </si>
-  <si>
-    <t>510052</t>
-  </si>
-  <si>
-    <t>ELMO CX02X05L</t>
-  </si>
-  <si>
-    <t>DUNNA CX02X05L</t>
-  </si>
-  <si>
-    <t>ARRANK CX02X05L</t>
-  </si>
-  <si>
-    <t>FB1324</t>
-  </si>
-  <si>
-    <t>FB1125</t>
-  </si>
-  <si>
-    <t>SKB0324.B</t>
-  </si>
-  <si>
-    <t>74604/26</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>X</t>
+    <t>DATA E LOTE DIVERGENTE</t>
+  </si>
+  <si>
+    <t>2 SACARIAS AVARIADAS</t>
+  </si>
+  <si>
+    <t>04945</t>
+  </si>
+  <si>
+    <t>05340</t>
+  </si>
+  <si>
+    <t>510009</t>
+  </si>
+  <si>
+    <t>SPEED SCX25KG</t>
+  </si>
+  <si>
+    <t>LOADER SCX20KG</t>
+  </si>
+  <si>
+    <t>BOROMAG CX02X10KG</t>
+  </si>
+  <si>
+    <t>Lote WMS</t>
+  </si>
+  <si>
+    <t>75646/26</t>
+  </si>
+  <si>
+    <t>74797/26</t>
+  </si>
+  <si>
+    <t>75574/26</t>
+  </si>
+  <si>
+    <t>75720/26</t>
+  </si>
+  <si>
+    <t>70809/25</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -934,19 +934,19 @@
         <v>53</v>
       </c>
       <c r="B2" s="17">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>50</v>
@@ -955,68 +955,68 @@
         <v>51</v>
       </c>
       <c r="I2" s="17">
-        <v>10778</v>
+        <v>10810</v>
       </c>
       <c r="J2" s="18">
-        <v>45551</v>
+        <v>45482</v>
       </c>
       <c r="K2" s="18">
-        <v>46108</v>
+        <v>46212</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M2" s="18">
-        <v>45551</v>
+        <v>46100</v>
       </c>
       <c r="N2" s="18">
-        <v>46108</v>
+        <v>47196</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P2" s="19">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="Q2" s="17" t="s">
         <v>67</v>
       </c>
       <c r="R2" s="17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="S2" s="20" t="s">
         <v>68</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="U2" s="17" t="s">
         <v>52</v>
       </c>
       <c r="V2" s="10" t="str">
         <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>AVARIA</v>
+        <v>PROCESSO</v>
       </c>
       <c r="W2"/>
     </row>
     <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="17">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G3" s="17" t="s">
         <v>50</v>
@@ -1025,68 +1025,68 @@
         <v>51</v>
       </c>
       <c r="I3" s="17">
-        <v>10778</v>
+        <v>10810</v>
       </c>
       <c r="J3" s="18">
-        <v>45900</v>
+        <v>45482</v>
       </c>
       <c r="K3" s="18">
-        <v>46446</v>
+        <v>46212</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="M3" s="18">
-        <v>45900</v>
+        <v>46094</v>
       </c>
       <c r="N3" s="18">
-        <v>46446</v>
+        <v>47190</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P3" s="19">
-        <v>160</v>
+        <v>2500</v>
       </c>
       <c r="Q3" s="17" t="s">
         <v>67</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="S3" s="20" t="s">
         <v>68</v>
       </c>
       <c r="T3" s="17" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="U3" s="17" t="s">
         <v>52</v>
       </c>
       <c r="V3" s="10" t="str">
         <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>AVARIA</v>
+        <v>PROCESSO</v>
       </c>
       <c r="W3"/>
     </row>
     <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B4" s="17">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>50</v>
@@ -1095,68 +1095,68 @@
         <v>51</v>
       </c>
       <c r="I4" s="17">
-        <v>10778</v>
+        <v>10810</v>
       </c>
       <c r="J4" s="18">
-        <v>45505</v>
+        <v>45482</v>
       </c>
       <c r="K4" s="18">
-        <v>46108</v>
+        <v>46212</v>
       </c>
       <c r="L4" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="M4" s="18">
-        <v>45505</v>
+        <v>46101</v>
       </c>
       <c r="N4" s="18">
-        <v>46108</v>
+        <v>47197</v>
       </c>
       <c r="O4" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P4" s="19">
-        <v>115</v>
+        <v>2500</v>
       </c>
       <c r="Q4" s="17" t="s">
         <v>67</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="S4" s="20" t="s">
         <v>68</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U4" s="17" t="s">
         <v>52</v>
       </c>
       <c r="V4" s="10" t="str">
         <f>IF(B4="",0,VLOOKUP(T4,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v xml:space="preserve">EMBALAGEM </v>
+        <v>PROCESSO</v>
       </c>
       <c r="W4"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="17">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>49</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>50</v>
@@ -1165,75 +1165,117 @@
         <v>51</v>
       </c>
       <c r="I5" s="17">
-        <v>10778</v>
+        <v>10810</v>
       </c>
       <c r="J5" s="18">
-        <v>46090</v>
+        <v>45985</v>
       </c>
       <c r="K5" s="18">
-        <v>46821</v>
+        <v>2958465</v>
       </c>
       <c r="L5" s="16" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="M5" s="18">
-        <v>46090</v>
+        <v>46106</v>
       </c>
       <c r="N5" s="18">
-        <v>47186</v>
+        <v>47202</v>
       </c>
       <c r="O5" s="16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P5" s="19">
-        <v>10800</v>
+        <v>9000</v>
       </c>
       <c r="Q5" s="17" t="s">
         <v>67</v>
       </c>
       <c r="R5" s="17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="S5" s="20" t="s">
         <v>68</v>
       </c>
       <c r="T5" s="17" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="U5" s="17" t="s">
         <v>52</v>
       </c>
       <c r="V5" s="10" t="str">
         <f>IF(B5="",0,VLOOKUP(T5,Planilha1!$A$2:$B$14,2,FALSE))</f>
+        <v>AVARIA</v>
+      </c>
+      <c r="W5"/>
+    </row>
+    <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="23">
+        <v>367</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="23">
+        <v>10810</v>
+      </c>
+      <c r="J6" s="25">
+        <v>45756</v>
+      </c>
+      <c r="K6" s="25">
+        <v>2958465</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="25">
+        <v>45901</v>
+      </c>
+      <c r="N6" s="25">
+        <v>46997</v>
+      </c>
+      <c r="O6" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="P6" s="26">
+        <v>4900</v>
+      </c>
+      <c r="Q6" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="R6" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="S6" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="T6" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="U6" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="V6" s="28" t="str">
+        <f>IF(B6="",0,VLOOKUP(T6,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>PROCESSO</v>
-      </c>
-      <c r="W5"/>
-    </row>
-    <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="28">
-        <f>IF(B6="",0,VLOOKUP(T6,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
       </c>
       <c r="W6"/>
     </row>

--- a/Plan_RNC.xlsx
+++ b/Plan_RNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\RNC-RA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48DC7E4-1854-4E14-B3DD-8E43EB314D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF7103E-7929-42B4-A8F0-B6C7FD12A4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16200" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
   <si>
     <t>NUMERO-NF</t>
   </si>
@@ -207,67 +207,70 @@
     <t>RESUMO-RAPIDO</t>
   </si>
   <si>
-    <t>RNC-01</t>
-  </si>
-  <si>
     <t>Hortolândia</t>
   </si>
   <si>
-    <t>VZP TRANSF HORT</t>
-  </si>
-  <si>
     <t>VZP NITRO</t>
   </si>
   <si>
     <t>NITRO</t>
   </si>
   <si>
-    <t>DATA E LOTE DIVERGENTE</t>
-  </si>
-  <si>
-    <t>2 SACARIAS AVARIADAS</t>
-  </si>
-  <si>
-    <t>04945</t>
-  </si>
-  <si>
-    <t>05340</t>
-  </si>
-  <si>
-    <t>510009</t>
-  </si>
-  <si>
-    <t>SPEED SCX25KG</t>
-  </si>
-  <si>
-    <t>LOADER SCX20KG</t>
-  </si>
-  <si>
-    <t>BOROMAG CX02X10KG</t>
-  </si>
-  <si>
-    <t>Lote WMS</t>
-  </si>
-  <si>
-    <t>75646/26</t>
-  </si>
-  <si>
-    <t>74797/26</t>
-  </si>
-  <si>
-    <t>75574/26</t>
-  </si>
-  <si>
-    <t>75720/26</t>
-  </si>
-  <si>
-    <t>70809/25</t>
-  </si>
-  <si>
     <t>KG</t>
   </si>
   <si>
-    <t>x</t>
+    <t>rnc01</t>
+  </si>
+  <si>
+    <t>rnc02</t>
+  </si>
+  <si>
+    <t>510018</t>
+  </si>
+  <si>
+    <t>260014</t>
+  </si>
+  <si>
+    <t>DEVOLUÇÃO</t>
+  </si>
+  <si>
+    <t>DEVOLUÇÃO CLIENTE</t>
+  </si>
+  <si>
+    <t>DUAS CAIXAS AVARIADAS</t>
+  </si>
+  <si>
+    <t>BOUVERIZ WP PRO N CX10X01KG</t>
+  </si>
+  <si>
+    <t>Durante o processo de recebimento da devolução, foi identificada a seguinte não conformidade: A) O produto BOUVERIZ WP PRO N CX10X01KG (NF 11041, Lote 260014) apresentou 02 caixas avariadas. Embora o dano físico tenha sido constatado no ato da descarga, ressalta-se que não foram anexadas evidências fotográficas ao e-mail de aviso/instrução, o que pode dificultar a análise de causa raiz e a contestação junto à transportadora ou ao cliente. O material foi segregado para pesagem e conferência da integridade dos pacotes internos de 1kg.</t>
+  </si>
+  <si>
+    <t>DATA DE VALIDADE DIVERGENTE</t>
+  </si>
+  <si>
+    <t>04857</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>REVITA 1000L</t>
+  </si>
+  <si>
+    <t>VZP TRANSF CBA</t>
+  </si>
+  <si>
+    <t>75392/26</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>IBC</t>
+  </si>
+  <si>
+    <t>Durante o processo de recebimento de transferência, transportado pela Fantinato, foi identificada a seguinte inconsistência de rastreabilidade: A) O produto REVITA 1000L (NF 10833, Lote 75392/26), totalizando 3.000L (03 IBCs), apresentou divergência na data de validade. No ato da conferência física, constatou-se que a validade impressa nos tanques não condiz com a informação registrada na Nota Fiscal. O material foi segregado e bloqueado para que o setor responsável realize a correção documental ou a reetiquetagem conforme as normas de qualidade.</t>
   </si>
 </sst>
 </file>
@@ -931,137 +934,137 @@
     </row>
     <row r="2" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="17" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B2" s="17">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C2" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="F2" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="17">
+        <v>11041</v>
+      </c>
+      <c r="J2" s="18">
+        <v>46070</v>
+      </c>
+      <c r="K2" s="18">
+        <v>46435</v>
+      </c>
+      <c r="L2" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="17" t="s">
+      <c r="M2" s="18">
+        <v>46070</v>
+      </c>
+      <c r="N2" s="18">
+        <v>46435</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" s="19">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I2" s="17">
-        <v>10810</v>
-      </c>
-      <c r="J2" s="18">
-        <v>45482</v>
-      </c>
-      <c r="K2" s="18">
-        <v>46212</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" s="18">
-        <v>46100</v>
-      </c>
-      <c r="N2" s="18">
-        <v>47196</v>
-      </c>
-      <c r="O2" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="P2" s="19">
-        <v>5000</v>
-      </c>
-      <c r="Q2" s="17" t="s">
-        <v>67</v>
-      </c>
       <c r="R2" s="17" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="S2" s="20" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="V2" s="10" t="str">
         <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
+        <v>AVARIA</v>
       </c>
       <c r="W2"/>
     </row>
     <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="17">
+        <v>371</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="17">
-        <v>367</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>48</v>
-      </c>
       <c r="D3" s="16" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E3" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="H3" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F3" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>51</v>
-      </c>
       <c r="I3" s="17">
-        <v>10810</v>
+        <v>10833</v>
       </c>
       <c r="J3" s="18">
-        <v>45482</v>
+        <v>46099</v>
       </c>
       <c r="K3" s="18">
-        <v>46212</v>
+        <v>46830</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="M3" s="18">
-        <v>46094</v>
+        <v>46099</v>
       </c>
       <c r="N3" s="18">
-        <v>47190</v>
+        <v>47195</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P3" s="19">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="Q3" s="17" t="s">
         <v>67</v>
       </c>
       <c r="R3" s="17" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="S3" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T3" s="17" t="s">
         <v>17</v>
       </c>
       <c r="U3" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V3" s="10" t="str">
         <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
@@ -1070,212 +1073,86 @@
       <c r="W3"/>
     </row>
     <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="B4" s="17">
-        <v>367</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="17">
-        <v>10810</v>
-      </c>
-      <c r="J4" s="18">
-        <v>45482</v>
-      </c>
-      <c r="K4" s="18">
-        <v>46212</v>
-      </c>
-      <c r="L4" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M4" s="18">
-        <v>46101</v>
-      </c>
-      <c r="N4" s="18">
-        <v>47197</v>
-      </c>
-      <c r="O4" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="P4" s="19">
-        <v>2500</v>
-      </c>
-      <c r="Q4" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="R4" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="T4" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="U4" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="V4" s="10" t="str">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="10">
         <f>IF(B4="",0,VLOOKUP(T4,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
+        <v>0</v>
       </c>
       <c r="W4"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="17">
-        <v>367</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" s="17">
-        <v>10810</v>
-      </c>
-      <c r="J5" s="18">
-        <v>45985</v>
-      </c>
-      <c r="K5" s="18">
-        <v>2958465</v>
-      </c>
-      <c r="L5" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="18">
-        <v>46106</v>
-      </c>
-      <c r="N5" s="18">
-        <v>47202</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="P5" s="19">
-        <v>9000</v>
-      </c>
-      <c r="Q5" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="R5" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="T5" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="U5" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="V5" s="10" t="str">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="10">
         <f>IF(B5="",0,VLOOKUP(T5,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>AVARIA</v>
+        <v>0</v>
       </c>
       <c r="W5"/>
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="23">
-        <v>367</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="23">
-        <v>10810</v>
-      </c>
-      <c r="J6" s="25">
-        <v>45756</v>
-      </c>
-      <c r="K6" s="25">
-        <v>2958465</v>
-      </c>
-      <c r="L6" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="M6" s="25">
-        <v>45901</v>
-      </c>
-      <c r="N6" s="25">
-        <v>46997</v>
-      </c>
-      <c r="O6" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="P6" s="26">
-        <v>4900</v>
-      </c>
-      <c r="Q6" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="R6" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="S6" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="T6" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="U6" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="V6" s="28" t="str">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="28">
         <f>IF(B6="",0,VLOOKUP(T6,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
+        <v>0</v>
       </c>
       <c r="W6"/>
     </row>
@@ -1469,7 +1346,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -1482,7 +1358,7 @@
       <formula1>"NITRO, FORNECEDOR, DEVOLUÇÃO"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R13" xr:uid="{9224D280-D2F8-4702-BD9E-3A2E00F78617}">
-      <formula1>"Saco, Bombona, Palete, Caixa, Big Bag, Galão"</formula1>
+      <formula1>"Saco, Bombona, Palete, Caixa, Big Bag, Galão, IBC"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G13" xr:uid="{0CCEE7D2-5A92-4296-95B7-680EA05B05B1}">
       <formula1>"VZP TRANSF HORT, DEVOLUÇÃO CLIENTE, VZP TRANSF CBA, RECEBIMENTO PORTO, ROO TRANSF HORT, ROO TRANSF CBA, HORT TRANSF CBA, TORRE DE CONTROLE, TRANSP. RODOFROTA, STZ TRANSF HORT, CBA TRANSF HORT, STZ TRANSF CBA, FORNECEDOR"</formula1>

--- a/Plan_RNC.xlsx
+++ b/Plan_RNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\RNC-RA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF7103E-7929-42B4-A8F0-B6C7FD12A4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4194376C-ED43-421E-83B0-9C856E7A2A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
   <si>
     <t>NUMERO-NF</t>
   </si>
@@ -207,70 +207,55 @@
     <t>RESUMO-RAPIDO</t>
   </si>
   <si>
-    <t>Hortolândia</t>
-  </si>
-  <si>
-    <t>VZP NITRO</t>
+    <t>rnc01</t>
+  </si>
+  <si>
+    <t>Cuiabá</t>
+  </si>
+  <si>
+    <t>CAIXA AMASSADA</t>
+  </si>
+  <si>
+    <t>EMBALAGEM MOLHADA</t>
+  </si>
+  <si>
+    <t>540138</t>
+  </si>
+  <si>
+    <t>04945</t>
+  </si>
+  <si>
+    <t>QUIRON CX04X05L</t>
+  </si>
+  <si>
+    <t>SPEED SCX25KG</t>
+  </si>
+  <si>
+    <t>HORT TRANSF CBA</t>
+  </si>
+  <si>
+    <t>HORT</t>
+  </si>
+  <si>
+    <t>003/2026-4200</t>
+  </si>
+  <si>
+    <t>74291/26</t>
+  </si>
+  <si>
+    <t>KG</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
   <si>
     <t>NITRO</t>
   </si>
   <si>
-    <t>KG</t>
-  </si>
-  <si>
-    <t>rnc01</t>
-  </si>
-  <si>
-    <t>rnc02</t>
-  </si>
-  <si>
-    <t>510018</t>
-  </si>
-  <si>
-    <t>260014</t>
-  </si>
-  <si>
-    <t>DEVOLUÇÃO</t>
-  </si>
-  <si>
-    <t>DEVOLUÇÃO CLIENTE</t>
-  </si>
-  <si>
-    <t>DUAS CAIXAS AVARIADAS</t>
-  </si>
-  <si>
-    <t>BOUVERIZ WP PRO N CX10X01KG</t>
-  </si>
-  <si>
-    <t>Durante o processo de recebimento da devolução, foi identificada a seguinte não conformidade: A) O produto BOUVERIZ WP PRO N CX10X01KG (NF 11041, Lote 260014) apresentou 02 caixas avariadas. Embora o dano físico tenha sido constatado no ato da descarga, ressalta-se que não foram anexadas evidências fotográficas ao e-mail de aviso/instrução, o que pode dificultar a análise de causa raiz e a contestação junto à transportadora ou ao cliente. O material foi segregado para pesagem e conferência da integridade dos pacotes internos de 1kg.</t>
-  </si>
-  <si>
-    <t>DATA DE VALIDADE DIVERGENTE</t>
-  </si>
-  <si>
-    <t>04857</t>
-  </si>
-  <si>
-    <t>Cuiabá</t>
-  </si>
-  <si>
-    <t>REVITA 1000L</t>
-  </si>
-  <si>
-    <t>VZP TRANSF CBA</t>
-  </si>
-  <si>
-    <t>75392/26</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>IBC</t>
-  </si>
-  <si>
-    <t>Durante o processo de recebimento de transferência, transportado pela Fantinato, foi identificada a seguinte inconsistência de rastreabilidade: A) O produto REVITA 1000L (NF 10833, Lote 75392/26), totalizando 3.000L (03 IBCs), apresentou divergência na data de validade. No ato da conferência física, constatou-se que a validade impressa nos tanques não condiz com a informação registrada na Nota Fiscal. O material foi segregado e bloqueado para que o setor responsável realize a correção documental ou a reetiquetagem conforme as normas de qualidade.</t>
+    <t xml:space="preserve">Durante o processo de recebimento de transferência, realizado pela transportadora Fantinato (NF 11057), foi identificada a seguinte não conformidade de integridade física: A) O produto QUIRON CX04X05L (Lote 003/2026-4200) apresentou avaria em parte da carga, totalizando 2.600L afetados. No momento da conferência, constatou-se que as embalagens secundárias (caixas) estavam amassadas. </t>
+  </si>
+  <si>
+    <t>Durante o processo de recebimento de transferência realizado pela transportadora Fantinato (NF 11057), foi identificada uma não conformidade crítica de conservação: B) O produto SPEED SCX25KG (Lote 74291/26), totalizando 25.000kg (carga completa), apresentou embalagens molhadas. No ato da descarga, constatou-se que a sacaria de papel/ráfia apresentava sinais de umidade excessiva. Por se tratar de um produto em pó/granulado, o contato com água compromete a integridade física do material (empedramento) e a resistência da embalagem, inviabilizando o armazenamento seguro e a comercialização.</t>
   </si>
 </sst>
 </file>
@@ -397,7 +382,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -431,6 +416,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -562,6 +553,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -864,13 +859,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="15" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="22" t="s">
         <v>40</v>
       </c>
       <c r="D1" s="22" t="s">
@@ -879,7 +874,7 @@
       <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="21" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="22" t="s">
@@ -888,7 +883,7 @@
       <c r="H1" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="J1" s="22" t="s">
@@ -897,7 +892,7 @@
       <c r="K1" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="21" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="22" t="s">
@@ -933,149 +928,149 @@
       <c r="W1" s="14"/>
     </row>
     <row r="2" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B2" s="17">
-        <v>370</v>
-      </c>
-      <c r="C2" s="17" t="s">
+      <c r="A2" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="29">
+        <v>372</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="E2" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>59</v>
-      </c>
       <c r="G2" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H2" s="17" t="s">
         <v>57</v>
       </c>
       <c r="I2" s="17">
-        <v>11041</v>
+        <v>11057</v>
       </c>
       <c r="J2" s="18">
-        <v>46070</v>
+        <v>46091</v>
       </c>
       <c r="K2" s="18">
-        <v>46435</v>
+        <v>46821</v>
       </c>
       <c r="L2" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="M2" s="18">
-        <v>46070</v>
+        <v>46091</v>
       </c>
       <c r="N2" s="18">
-        <v>46435</v>
+        <v>46821</v>
       </c>
       <c r="O2" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P2" s="19">
-        <v>20</v>
+        <v>2600</v>
       </c>
       <c r="Q2" s="17" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="R2" s="17" t="s">
         <v>37</v>
       </c>
       <c r="S2" s="20" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="V2" s="10" t="str">
         <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>AVARIA</v>
+        <v xml:space="preserve">EMBALAGEM </v>
       </c>
       <c r="W2"/>
     </row>
     <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B3" s="17">
-        <v>371</v>
-      </c>
-      <c r="C3" s="17" t="s">
+      <c r="A3" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="29">
+        <v>372</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="E3" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="17">
+        <v>11057</v>
+      </c>
+      <c r="J3" s="18">
+        <v>46051</v>
+      </c>
+      <c r="K3" s="18">
+        <v>47147</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="18">
+        <v>46051</v>
+      </c>
+      <c r="N3" s="18">
+        <v>47147</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="P3" s="19">
+        <v>25000</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="S3" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="T3" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="U3" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="H3" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="I3" s="17">
-        <v>10833</v>
-      </c>
-      <c r="J3" s="18">
-        <v>46099</v>
-      </c>
-      <c r="K3" s="18">
-        <v>46830</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="M3" s="18">
-        <v>46099</v>
-      </c>
-      <c r="N3" s="18">
-        <v>47195</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="P3" s="19">
-        <v>3000</v>
-      </c>
-      <c r="Q3" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="R3" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="S3" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="T3" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="17" t="s">
-        <v>50</v>
       </c>
       <c r="V3" s="10" t="str">
         <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>PROCESSO</v>
+        <v xml:space="preserve">EMBALAGEM </v>
       </c>
       <c r="W3"/>
     </row>
     <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
       <c r="D4" s="16"/>
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>
@@ -1101,9 +1096,9 @@
       <c r="W4"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
       <c r="D5" s="16"/>
       <c r="E5" s="17"/>
       <c r="F5" s="17"/>
@@ -1129,9 +1124,9 @@
       <c r="W5"/>
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
       <c r="D6" s="24"/>
       <c r="E6" s="23"/>
       <c r="F6" s="23"/>
@@ -1157,9 +1152,9 @@
       <c r="W6"/>
     </row>
     <row r="7" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
       <c r="D7" s="24"/>
       <c r="E7" s="23"/>
       <c r="F7" s="23"/>
@@ -1184,9 +1179,9 @@
       </c>
     </row>
     <row r="8" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23"/>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
       <c r="D8" s="24"/>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -1211,9 +1206,9 @@
       </c>
     </row>
     <row r="9" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
+      <c r="A9" s="29"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="24"/>
       <c r="E9" s="23"/>
       <c r="F9" s="23"/>
@@ -1238,9 +1233,9 @@
       </c>
     </row>
     <row r="10" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="29"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="29"/>
       <c r="D10" s="16"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17"/>
@@ -1265,9 +1260,9 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="29"/>
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
       <c r="D11" s="16"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -1292,9 +1287,9 @@
       </c>
     </row>
     <row r="12" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="16"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
@@ -1319,9 +1314,9 @@
       </c>
     </row>
     <row r="13" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="16"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
@@ -1346,6 +1341,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="I1:I1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
@@ -1363,7 +1359,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G13" xr:uid="{0CCEE7D2-5A92-4296-95B7-680EA05B05B1}">
       <formula1>"VZP TRANSF HORT, DEVOLUÇÃO CLIENTE, VZP TRANSF CBA, RECEBIMENTO PORTO, ROO TRANSF HORT, ROO TRANSF CBA, HORT TRANSF CBA, TORRE DE CONTROLE, TRANSP. RODOFROTA, STZ TRANSF HORT, CBA TRANSF HORT, STZ TRANSF CBA, FORNECEDOR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G13 E2:E13" xr:uid="{A9DDEBF6-CC05-4C4C-B66F-05CC7D4CAF45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E13 G2:G13" xr:uid="{A9DDEBF6-CC05-4C4C-B66F-05CC7D4CAF45}">
       <formula1>"Cuiabá, Hortolândia"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H13" xr:uid="{EE69AD02-7E08-441A-857C-3BD9A1515FF8}">

--- a/Plan_RNC.xlsx
+++ b/Plan_RNC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iesus.candido\Desktop\RNC-RA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4194376C-ED43-421E-83B0-9C856E7A2A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F33A38C-45D7-4A7E-AA84-1B3F30E7F803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33630" yWindow="-1305" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="76">
   <si>
     <t>NUMERO-NF</t>
   </si>
@@ -207,55 +207,88 @@
     <t>RESUMO-RAPIDO</t>
   </si>
   <si>
-    <t>rnc01</t>
+    <t>RC01</t>
+  </si>
+  <si>
+    <t>RC02</t>
+  </si>
+  <si>
+    <t>RC03</t>
+  </si>
+  <si>
+    <t>Embalagem amassada e suja</t>
+  </si>
+  <si>
+    <t>00076-1</t>
+  </si>
+  <si>
+    <t>Hortolândia</t>
   </si>
   <si>
     <t>Cuiabá</t>
   </si>
   <si>
-    <t>CAIXA AMASSADA</t>
-  </si>
-  <si>
-    <t>EMBALAGEM MOLHADA</t>
-  </si>
-  <si>
-    <t>540138</t>
-  </si>
-  <si>
-    <t>04945</t>
-  </si>
-  <si>
-    <t>QUIRON CX04X05L</t>
-  </si>
-  <si>
-    <t>SPEED SCX25KG</t>
-  </si>
-  <si>
-    <t>HORT TRANSF CBA</t>
-  </si>
-  <si>
-    <t>HORT</t>
-  </si>
-  <si>
-    <t>003/2026-4200</t>
-  </si>
-  <si>
-    <t>74291/26</t>
+    <t>NITRO 13 +N CX02X05L</t>
+  </si>
+  <si>
+    <t>VZP TRANSF CBA</t>
+  </si>
+  <si>
+    <t>VZP NITRO</t>
+  </si>
+  <si>
+    <t>75492/26</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durante o processo de transferência da carga, origem Várzea Paulista x Cuiabá, transportadora Fantinato, placa FRT8D77 foi identificada a seguinte não conformidade de qualidade e integridade: A) O produto NITRO 13 +N CX02X05L (Lote 75492/26) apresentou caixas amassadas e um pó amarelo em todos os paletes. </t>
+  </si>
+  <si>
+    <t>NITRO</t>
+  </si>
+  <si>
+    <t>Sacarias rasgadas</t>
+  </si>
+  <si>
+    <t>510002</t>
+  </si>
+  <si>
+    <t>SPEED CANA SCX25KG</t>
+  </si>
+  <si>
+    <t>VZP TRANSF HORT</t>
+  </si>
+  <si>
+    <t>76181/26</t>
   </si>
   <si>
     <t>KG</t>
   </si>
   <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>NITRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Durante o processo de recebimento de transferência, realizado pela transportadora Fantinato (NF 11057), foi identificada a seguinte não conformidade de integridade física: A) O produto QUIRON CX04X05L (Lote 003/2026-4200) apresentou avaria em parte da carga, totalizando 2.600L afetados. No momento da conferência, constatou-se que as embalagens secundárias (caixas) estavam amassadas. </t>
-  </si>
-  <si>
-    <t>Durante o processo de recebimento de transferência realizado pela transportadora Fantinato (NF 11057), foi identificada uma não conformidade crítica de conservação: B) O produto SPEED SCX25KG (Lote 74291/26), totalizando 25.000kg (carga completa), apresentou embalagens molhadas. No ato da descarga, constatou-se que a sacaria de papel/ráfia apresentava sinais de umidade excessiva. Por se tratar de um produto em pó/granulado, o contato com água compromete a integridade física do material (empedramento) e a resistência da embalagem, inviabilizando o armazenamento seguro e a comercialização.</t>
+    <t>Durante o processo de descarga da transferência, VZP e Hortolândia (NF 10996), transportadora MMCM, veículo placa CSK4B33, foi identificada a seguinte não conformidade física: A) O produto SPEED CANA SCX25KG (Lote 76181/26) apresentou avaria em 02 sacarias, totalizando 50kg. No ato do recebimento, as embalagens foram encontradas rasgadas. O volume foi imediatamente segregado.</t>
+  </si>
+  <si>
+    <t>Falta/caixas amassadas/rasgadas e sujas</t>
+  </si>
+  <si>
+    <t>03020266</t>
+  </si>
+  <si>
+    <t>LOADER C/10 KG</t>
+  </si>
+  <si>
+    <t>DEVOLUÇÃO CLIENTE</t>
+  </si>
+  <si>
+    <t>70459/25</t>
+  </si>
+  <si>
+    <t>Durante o processo de descarga da devolução (NF 6652), cliente GFP Agrícola Ltda, transportado pela Transouza (Placa QIF4A25) foram identificadas múltiplas não conformidades de integridade e quantidade: 1) Avaria Física: O produto LOADER (Lote 70459/25) apresentou caixas amassadas, rasgadas e com sujidade. O estado das embalagens secundárias compromete a segurança do empilhamento e a apresentação comercial do produto. 2) Falta de Mercadoria: No ato da conferência física dos 740kg declarados, constatou-se uma falta de 10kg em relação ao peso constante na Nota Fiscal 750kg.</t>
+  </si>
+  <si>
+    <t>DEVOLUÇÃO</t>
   </si>
 </sst>
 </file>
@@ -521,10 +554,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="49" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -547,15 +576,19 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -859,67 +892,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="15" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="J1" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="M1" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="N1" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="O1" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="P1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="Q1" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="R1" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="S1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="T1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="U1" s="22" t="s">
+      <c r="U1" s="21" t="s">
         <v>32</v>
       </c>
       <c r="V1" s="13" t="s">
@@ -928,23 +961,23 @@
       <c r="W1" s="14"/>
     </row>
     <row r="2" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="29">
-        <v>372</v>
-      </c>
-      <c r="C2" s="29" t="s">
+      <c r="A2" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="27">
+        <v>376</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>48</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>52</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2" s="17" t="s">
         <v>56</v>
@@ -953,152 +986,194 @@
         <v>57</v>
       </c>
       <c r="I2" s="17">
-        <v>11057</v>
+        <v>10883</v>
       </c>
       <c r="J2" s="18">
-        <v>46091</v>
+        <v>46105</v>
       </c>
       <c r="K2" s="18">
-        <v>46821</v>
+        <v>47201</v>
       </c>
       <c r="L2" s="16" t="s">
         <v>58</v>
       </c>
       <c r="M2" s="18">
-        <v>46091</v>
+        <v>46118</v>
       </c>
       <c r="N2" s="18">
-        <v>46821</v>
+        <v>47214</v>
       </c>
       <c r="O2" s="16" t="s">
         <v>58</v>
       </c>
       <c r="P2" s="19">
-        <v>2600</v>
+        <v>720</v>
       </c>
       <c r="Q2" s="17" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="R2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="S2" s="20" t="s">
-        <v>63</v>
+      <c r="S2" s="28" t="s">
+        <v>60</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V2" s="10" t="str">
         <f>IF(B2="",0,VLOOKUP(T2,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v xml:space="preserve">EMBALAGEM </v>
+        <v>PROCESSO</v>
       </c>
       <c r="W2"/>
     </row>
     <row r="3" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="29">
-        <v>372</v>
-      </c>
-      <c r="C3" s="29" t="s">
-        <v>48</v>
+      <c r="A3" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="27">
+        <v>377</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>49</v>
       </c>
       <c r="D3" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>49</v>
-      </c>
       <c r="F3" s="17" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="H3" s="17" t="s">
         <v>57</v>
       </c>
       <c r="I3" s="17">
-        <v>11057</v>
+        <v>10996</v>
       </c>
       <c r="J3" s="18">
-        <v>46051</v>
+        <v>46127</v>
       </c>
       <c r="K3" s="18">
-        <v>47147</v>
+        <v>47223</v>
       </c>
       <c r="L3" s="16" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="M3" s="18">
-        <v>46051</v>
+        <v>46127</v>
       </c>
       <c r="N3" s="18">
-        <v>47147</v>
+        <v>47223</v>
       </c>
       <c r="O3" s="16" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="P3" s="19">
-        <v>25000</v>
+        <v>720</v>
       </c>
       <c r="Q3" s="17" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="R3" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="S3" s="20" t="s">
-        <v>64</v>
+      <c r="S3" s="28" t="s">
+        <v>68</v>
       </c>
       <c r="T3" s="17" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U3" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="V3" s="10" t="str">
         <f>IF(B3="",0,VLOOKUP(T3,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v xml:space="preserve">EMBALAGEM </v>
+        <v>AVARIA</v>
       </c>
       <c r="W3"/>
     </row>
     <row r="4" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="17"/>
-      <c r="U4" s="17"/>
-      <c r="V4" s="10">
+      <c r="A4" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="27">
+        <v>378</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="I4" s="17">
+        <v>6652</v>
+      </c>
+      <c r="J4" s="18">
+        <v>45888</v>
+      </c>
+      <c r="K4" s="18">
+        <v>46984</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="18">
+        <v>45888</v>
+      </c>
+      <c r="N4" s="18">
+        <v>46984</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="P4" s="19">
+        <v>740</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="S4" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="V4" s="10" t="str">
         <f>IF(B4="",0,VLOOKUP(T4,Planilha1!$A$2:$B$14,2,FALSE))</f>
-        <v>0</v>
+        <v>PROCESSO</v>
       </c>
       <c r="W4"/>
     </row>
     <row r="5" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
+      <c r="A5" s="27"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="16"/>
       <c r="E5" s="17"/>
       <c r="F5" s="17"/>
@@ -1114,7 +1189,7 @@
       <c r="P5" s="19"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="17"/>
-      <c r="S5" s="20"/>
+      <c r="S5" s="28"/>
       <c r="T5" s="17"/>
       <c r="U5" s="17"/>
       <c r="V5" s="10">
@@ -1124,118 +1199,118 @@
       <c r="W5"/>
     </row>
     <row r="6" spans="1:23" s="9" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="26"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="28">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="25"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="26">
         <f>IF(B6="",0,VLOOKUP(T6,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
       <c r="W6"/>
     </row>
     <row r="7" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="29"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23"/>
-      <c r="G7" s="23"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="26"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="27"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="28">
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="26">
         <f>IF(B7="",0,VLOOKUP(T7,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23"/>
-      <c r="I8" s="23"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="26"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="28">
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="26">
         <f>IF(B8="",0,VLOOKUP(T8,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="23"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="23"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="28">
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="26">
         <f>IF(B9="",0,VLOOKUP(T9,Planilha1!$A$2:$B$14,2,FALSE))</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
+      <c r="A10" s="27"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
       <c r="D10" s="16"/>
       <c r="E10" s="17"/>
       <c r="F10" s="17"/>
@@ -1251,7 +1326,7 @@
       <c r="P10" s="19"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="17"/>
-      <c r="S10" s="20"/>
+      <c r="S10" s="28"/>
       <c r="T10" s="17"/>
       <c r="U10" s="17"/>
       <c r="V10" s="10">
@@ -1260,9 +1335,9 @@
       </c>
     </row>
     <row r="11" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="16"/>
       <c r="E11" s="17"/>
       <c r="F11" s="17"/>
@@ -1278,7 +1353,7 @@
       <c r="P11" s="19"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="17"/>
-      <c r="S11" s="20"/>
+      <c r="S11" s="28"/>
       <c r="T11" s="17"/>
       <c r="U11" s="17"/>
       <c r="V11" s="10">
@@ -1287,9 +1362,9 @@
       </c>
     </row>
     <row r="12" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
       <c r="D12" s="16"/>
       <c r="E12" s="17"/>
       <c r="F12" s="17"/>
@@ -1305,7 +1380,7 @@
       <c r="P12" s="19"/>
       <c r="Q12" s="17"/>
       <c r="R12" s="17"/>
-      <c r="S12" s="20"/>
+      <c r="S12" s="28"/>
       <c r="T12" s="17"/>
       <c r="U12" s="17"/>
       <c r="V12" s="10">
@@ -1314,9 +1389,9 @@
       </c>
     </row>
     <row r="13" spans="1:23" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
       <c r="D13" s="16"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
@@ -1332,7 +1407,7 @@
       <c r="P13" s="19"/>
       <c r="Q13" s="17"/>
       <c r="R13" s="17"/>
-      <c r="S13" s="20"/>
+      <c r="S13" s="28"/>
       <c r="T13" s="17"/>
       <c r="U13" s="17"/>
       <c r="V13" s="10">
